--- a/Backend/srvdata/T-MAXeeprom.xlsx
+++ b/Backend/srvdata/T-MAXeeprom.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="524">
   <si>
     <t>EEPROM定义_V1.0_20231027</t>
   </si>
@@ -248,6 +248,9 @@
     <t>/*量程1*/</t>
   </si>
   <si>
+    <t>double</t>
+  </si>
+  <si>
     <t>5,10</t>
   </si>
   <si>
@@ -276,6 +279,9 @@
   </si>
   <si>
     <t>1,2,5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value：1, 2, 5 ,10 </t>
   </si>
   <si>
     <t>分度值2</t>
@@ -349,6 +355,9 @@
     <t>/*单位kg  */</t>
   </si>
   <si>
+    <t>0.OFF，1.ON</t>
+  </si>
+  <si>
     <t>单位g</t>
   </si>
   <si>
@@ -632,6 +641,9 @@
     <t>/*出厂序号*/</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>默认参数标志</t>
   </si>
   <si>
@@ -1442,6 +1454,9 @@
     <t>/*机型名*/</t>
   </si>
   <si>
+    <t>Model name</t>
+  </si>
+  <si>
     <t>（输入的机型名，供打印使用）</t>
   </si>
   <si>
@@ -1452,6 +1467,9 @@
   </si>
   <si>
     <t>/*秤名*/</t>
+  </si>
+  <si>
+    <t>Scale name</t>
   </si>
   <si>
     <t>（输入的秤名，仅供打印使用）</t>
@@ -3761,19 +3779,19 @@
         <v>61</v>
       </c>
       <c r="K19" s="12" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="L19" s="12">
         <v>1</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N19" s="12" t="s">
         <v>13</v>
       </c>
       <c r="O19" s="30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P19" s="31"/>
     </row>
@@ -3782,10 +3800,10 @@
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
       <c r="D20" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F20" s="21">
         <v>4</v>
@@ -3798,26 +3816,26 @@
         <v>41</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J20" s="12">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
       <c r="K20" s="12" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="L20" s="12">
         <v>1</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N20" s="12" t="s">
         <v>13</v>
       </c>
       <c r="O20" s="30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P20" s="31"/>
     </row>
@@ -3826,10 +3844,10 @@
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
       <c r="D21" s="19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F21" s="21">
         <v>1</v>
@@ -3842,7 +3860,7 @@
         <v>45</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J21" s="12">
         <f t="shared" si="1"/>
@@ -3855,10 +3873,10 @@
         <v>1</v>
       </c>
       <c r="M21" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="O21" s="30"/>
       <c r="P21" s="31"/>
@@ -3868,10 +3886,10 @@
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
       <c r="D22" s="19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22" s="21">
         <v>1</v>
@@ -3884,7 +3902,7 @@
         <v>46</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J22" s="12">
         <f t="shared" si="1"/>
@@ -3897,10 +3915,10 @@
         <v>1</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="O22" s="30"/>
       <c r="P22" s="31"/>
@@ -3910,10 +3928,10 @@
       <c r="B23" s="17"/>
       <c r="C23" s="18"/>
       <c r="D23" s="19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F23" s="21">
         <v>1</v>
@@ -3926,7 +3944,7 @@
         <v>47</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J23" s="12">
         <f t="shared" si="1"/>
@@ -3939,13 +3957,13 @@
         <v>1</v>
       </c>
       <c r="M23" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N23" s="12" t="s">
         <v>13</v>
       </c>
       <c r="O23" s="32" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P23" s="31"/>
     </row>
@@ -3954,10 +3972,10 @@
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
       <c r="D24" s="19" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F24" s="21">
         <v>1</v>
@@ -3970,7 +3988,7 @@
         <v>48</v>
       </c>
       <c r="I24" s="24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J24" s="12">
         <f t="shared" si="1"/>
@@ -3989,7 +4007,7 @@
         <v>13</v>
       </c>
       <c r="O24" s="30" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="P24" s="31"/>
     </row>
@@ -3998,10 +4016,10 @@
       <c r="B25" s="17"/>
       <c r="C25" s="18"/>
       <c r="D25" s="19" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F25" s="21">
         <v>1</v>
@@ -4014,7 +4032,7 @@
         <v>49</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J25" s="12">
         <f t="shared" si="1"/>
@@ -4024,13 +4042,13 @@
         <v>21</v>
       </c>
       <c r="L25" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25" s="12">
         <v>1</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O25" s="30"/>
       <c r="P25" s="31"/>
@@ -4040,10 +4058,10 @@
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
       <c r="D26" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F26" s="21">
         <v>1</v>
@@ -4056,7 +4074,7 @@
         <v>4A</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J26" s="12">
         <f t="shared" si="1"/>
@@ -4066,13 +4084,13 @@
         <v>21</v>
       </c>
       <c r="L26" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="12">
         <v>1</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O26" s="30"/>
       <c r="P26" s="31"/>
@@ -4082,10 +4100,10 @@
       <c r="B27" s="17"/>
       <c r="C27" s="18"/>
       <c r="D27" s="19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F27" s="21">
         <v>1</v>
@@ -4098,7 +4116,7 @@
         <v>4B</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="J27" s="12">
         <f t="shared" si="1"/>
@@ -4108,13 +4126,13 @@
         <v>21</v>
       </c>
       <c r="L27" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" s="12">
         <v>1</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O27" s="30"/>
       <c r="P27" s="31"/>
@@ -4124,10 +4142,10 @@
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
       <c r="D28" s="19" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F28" s="21">
         <v>1</v>
@@ -4140,7 +4158,7 @@
         <v>4C</v>
       </c>
       <c r="I28" s="24" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J28" s="12">
         <f t="shared" si="1"/>
@@ -4150,13 +4168,13 @@
         <v>21</v>
       </c>
       <c r="L28" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" s="12">
         <v>1</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O28" s="30"/>
       <c r="P28" s="31"/>
@@ -4166,10 +4184,10 @@
       <c r="B29" s="17"/>
       <c r="C29" s="18"/>
       <c r="D29" s="19" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F29" s="21">
         <v>1</v>
@@ -4182,7 +4200,7 @@
         <v>4D</v>
       </c>
       <c r="I29" s="24" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J29" s="12">
         <f t="shared" si="1"/>
@@ -4192,13 +4210,13 @@
         <v>21</v>
       </c>
       <c r="L29" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M29" s="12">
         <v>1</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O29" s="30"/>
       <c r="P29" s="31"/>
@@ -4208,10 +4226,10 @@
       <c r="B30" s="17"/>
       <c r="C30" s="18"/>
       <c r="D30" s="19" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F30" s="21">
         <v>1</v>
@@ -4224,7 +4242,7 @@
         <v>4E</v>
       </c>
       <c r="I30" s="24" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J30" s="12">
         <f t="shared" si="1"/>
@@ -4234,13 +4252,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" s="12">
         <v>1</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O30" s="30"/>
       <c r="P30" s="31"/>
@@ -4250,10 +4268,10 @@
       <c r="B31" s="17"/>
       <c r="C31" s="18"/>
       <c r="D31" s="19" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F31" s="21">
         <v>1</v>
@@ -4266,7 +4284,7 @@
         <v>4F</v>
       </c>
       <c r="I31" s="24" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J31" s="12">
         <f t="shared" si="1"/>
@@ -4276,13 +4294,13 @@
         <v>21</v>
       </c>
       <c r="L31" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M31" s="12">
         <v>1</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O31" s="30"/>
       <c r="P31" s="31"/>
@@ -4292,10 +4310,10 @@
       <c r="B32" s="17"/>
       <c r="C32" s="18"/>
       <c r="D32" s="19" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F32" s="21">
         <v>1</v>
@@ -4308,7 +4326,7 @@
         <v>50</v>
       </c>
       <c r="I32" s="24" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J32" s="12">
         <f t="shared" si="1"/>
@@ -4318,13 +4336,13 @@
         <v>21</v>
       </c>
       <c r="L32" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M32" s="12">
         <v>1</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O32" s="30"/>
       <c r="P32" s="31"/>
@@ -4334,10 +4352,10 @@
       <c r="B33" s="17"/>
       <c r="C33" s="18"/>
       <c r="D33" s="19" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F33" s="21">
         <v>1</v>
@@ -4350,7 +4368,7 @@
         <v>51</v>
       </c>
       <c r="I33" s="24" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J33" s="12">
         <f t="shared" si="1"/>
@@ -4360,13 +4378,13 @@
         <v>21</v>
       </c>
       <c r="L33" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" s="12">
         <v>1</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O33" s="30"/>
       <c r="P33" s="31"/>
@@ -4376,10 +4394,10 @@
       <c r="B34" s="17"/>
       <c r="C34" s="18"/>
       <c r="D34" s="19" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F34" s="21">
         <v>1</v>
@@ -4392,7 +4410,7 @@
         <v>52</v>
       </c>
       <c r="I34" s="24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J34" s="12">
         <f t="shared" si="1"/>
@@ -4402,13 +4420,13 @@
         <v>21</v>
       </c>
       <c r="L34" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M34" s="12">
         <v>1</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O34" s="30"/>
       <c r="P34" s="31"/>
@@ -4418,10 +4436,10 @@
       <c r="B35" s="17"/>
       <c r="C35" s="18"/>
       <c r="D35" s="19" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F35" s="21">
         <v>1</v>
@@ -4434,7 +4452,7 @@
         <v>53</v>
       </c>
       <c r="I35" s="24" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J35" s="12">
         <f t="shared" si="1"/>
@@ -4444,13 +4462,13 @@
         <v>21</v>
       </c>
       <c r="L35" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M35" s="12">
         <v>1</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O35" s="30"/>
       <c r="P35" s="31"/>
@@ -4460,10 +4478,10 @@
       <c r="B36" s="17"/>
       <c r="C36" s="18"/>
       <c r="D36" s="19" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F36" s="21">
         <v>1</v>
@@ -4476,7 +4494,7 @@
         <v>54</v>
       </c>
       <c r="I36" s="24" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J36" s="12">
         <f t="shared" si="1"/>
@@ -4486,13 +4504,13 @@
         <v>21</v>
       </c>
       <c r="L36" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M36" s="12">
         <v>1</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O36" s="30"/>
       <c r="P36" s="31"/>
@@ -4502,10 +4520,10 @@
       <c r="B37" s="17"/>
       <c r="C37" s="18"/>
       <c r="D37" s="19" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E37" s="20" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F37" s="21">
         <v>1</v>
@@ -4518,7 +4536,7 @@
         <v>55</v>
       </c>
       <c r="I37" s="24" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J37" s="12">
         <f t="shared" si="1"/>
@@ -4528,13 +4546,13 @@
         <v>21</v>
       </c>
       <c r="L37" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M37" s="12">
         <v>1</v>
       </c>
       <c r="N37" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O37" s="30"/>
       <c r="P37" s="31"/>
@@ -4544,10 +4562,10 @@
       <c r="B38" s="17"/>
       <c r="C38" s="18"/>
       <c r="D38" s="19" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F38" s="21">
         <v>1</v>
@@ -4560,7 +4578,7 @@
         <v>56</v>
       </c>
       <c r="I38" s="24" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J38" s="12">
         <f t="shared" si="1"/>
@@ -4570,13 +4588,13 @@
         <v>21</v>
       </c>
       <c r="L38" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38" s="12">
         <v>1</v>
       </c>
       <c r="N38" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O38" s="30"/>
       <c r="P38" s="31"/>
@@ -4586,10 +4604,10 @@
       <c r="B39" s="17"/>
       <c r="C39" s="18"/>
       <c r="D39" s="19" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E39" s="20" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F39" s="21">
         <v>1</v>
@@ -4602,7 +4620,7 @@
         <v>57</v>
       </c>
       <c r="I39" s="24" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J39" s="12">
         <f t="shared" si="1"/>
@@ -4612,13 +4630,13 @@
         <v>21</v>
       </c>
       <c r="L39" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M39" s="12">
         <v>1</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O39" s="30"/>
       <c r="P39" s="31"/>
@@ -4628,10 +4646,10 @@
       <c r="B40" s="17"/>
       <c r="C40" s="18"/>
       <c r="D40" s="19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F40" s="21">
         <v>1</v>
@@ -4644,7 +4662,7 @@
         <v>58</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J40" s="12">
         <f t="shared" si="1"/>
@@ -4654,13 +4672,13 @@
         <v>21</v>
       </c>
       <c r="L40" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M40" s="12">
         <v>1</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O40" s="30"/>
       <c r="P40" s="31"/>
@@ -4670,10 +4688,10 @@
       <c r="B41" s="17"/>
       <c r="C41" s="18"/>
       <c r="D41" s="19" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F41" s="21">
         <v>1</v>
@@ -4686,7 +4704,7 @@
         <v>59</v>
       </c>
       <c r="I41" s="24" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J41" s="12">
         <f t="shared" si="1"/>
@@ -4696,13 +4714,13 @@
         <v>21</v>
       </c>
       <c r="L41" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41" s="12">
         <v>1</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O41" s="30"/>
       <c r="P41" s="31"/>
@@ -4712,10 +4730,10 @@
       <c r="B42" s="17"/>
       <c r="C42" s="18"/>
       <c r="D42" s="19" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F42" s="21">
         <v>1</v>
@@ -4728,7 +4746,7 @@
         <v>5A</v>
       </c>
       <c r="I42" s="24" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J42" s="12">
         <f t="shared" si="1"/>
@@ -4738,13 +4756,13 @@
         <v>21</v>
       </c>
       <c r="L42" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M42" s="12">
         <v>1</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O42" s="30"/>
       <c r="P42" s="31"/>
@@ -4754,10 +4772,10 @@
       <c r="B43" s="17"/>
       <c r="C43" s="18"/>
       <c r="D43" s="19" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E43" s="20" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F43" s="21">
         <v>1</v>
@@ -4770,7 +4788,7 @@
         <v>5B</v>
       </c>
       <c r="I43" s="24" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J43" s="12">
         <f t="shared" si="1"/>
@@ -4780,13 +4798,13 @@
         <v>21</v>
       </c>
       <c r="L43" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M43" s="12">
         <v>1</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O43" s="30"/>
       <c r="P43" s="31"/>
@@ -4796,10 +4814,10 @@
       <c r="B44" s="17"/>
       <c r="C44" s="18"/>
       <c r="D44" s="19" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F44" s="21">
         <v>1</v>
@@ -4812,7 +4830,7 @@
         <v>5C</v>
       </c>
       <c r="I44" s="24" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J44" s="12">
         <f t="shared" si="1"/>
@@ -4822,13 +4840,13 @@
         <v>21</v>
       </c>
       <c r="L44" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" s="12">
         <v>1</v>
       </c>
       <c r="N44" s="12" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="O44" s="30"/>
       <c r="P44" s="31"/>
@@ -4838,10 +4856,10 @@
       <c r="B45" s="17"/>
       <c r="C45" s="18"/>
       <c r="D45" s="19" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E45" s="20" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F45" s="21">
         <v>1</v>
@@ -4854,7 +4872,7 @@
         <v>5D</v>
       </c>
       <c r="I45" s="24" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J45" s="12">
         <f t="shared" si="1"/>
@@ -4880,10 +4898,10 @@
       <c r="B46" s="17"/>
       <c r="C46" s="18"/>
       <c r="D46" s="19" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F46" s="21">
         <v>1</v>
@@ -4896,7 +4914,7 @@
         <v>5E</v>
       </c>
       <c r="I46" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J46" s="12">
         <f t="shared" si="1"/>
@@ -4922,10 +4940,10 @@
       <c r="B47" s="17"/>
       <c r="C47" s="18"/>
       <c r="D47" s="19" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E47" s="20" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F47" s="21">
         <v>1</v>
@@ -4938,7 +4956,7 @@
         <v>5F</v>
       </c>
       <c r="I47" s="24" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="J47" s="12">
         <f t="shared" si="1"/>
@@ -4964,10 +4982,10 @@
       <c r="B48" s="17"/>
       <c r="C48" s="18"/>
       <c r="D48" s="19" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F48" s="21">
         <v>2</v>
@@ -4980,7 +4998,7 @@
         <v>60</v>
       </c>
       <c r="I48" s="24" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J48" s="12">
         <f t="shared" si="1"/>
@@ -5006,10 +5024,10 @@
       <c r="B49" s="17"/>
       <c r="C49" s="18"/>
       <c r="D49" s="19" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F49" s="21">
         <v>1</v>
@@ -5022,7 +5040,7 @@
         <v>62</v>
       </c>
       <c r="I49" s="24" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J49" s="12">
         <f t="shared" si="1"/>
@@ -5048,10 +5066,10 @@
       <c r="B50" s="17"/>
       <c r="C50" s="18"/>
       <c r="D50" s="25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E50" s="25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F50" s="26">
         <v>4</v>
@@ -5086,17 +5104,17 @@
     <row r="51" ht="20.25" spans="1:16">
       <c r="A51" s="16"/>
       <c r="B51" s="16" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C51" s="28">
         <f>SUM(F81,J81)-J51</f>
         <v>62</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E51" s="20" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F51" s="21">
         <v>1</v>
@@ -5109,7 +5127,7 @@
         <v>67</v>
       </c>
       <c r="I51" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="J51" s="12">
         <f t="shared" si="1"/>
@@ -5135,10 +5153,10 @@
       <c r="B52" s="16"/>
       <c r="C52" s="28"/>
       <c r="D52" s="19" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F52" s="21">
         <v>15</v>
@@ -5151,14 +5169,14 @@
         <v>68</v>
       </c>
       <c r="I52" s="24" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J52" s="12">
         <f t="shared" si="1"/>
         <v>104</v>
       </c>
       <c r="K52" s="12" t="s">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="L52" s="12">
         <v>2</v>
@@ -5177,10 +5195,10 @@
       <c r="B53" s="16"/>
       <c r="C53" s="28"/>
       <c r="D53" s="19" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F53" s="21">
         <v>1</v>
@@ -5193,7 +5211,7 @@
         <v>77</v>
       </c>
       <c r="I53" s="24" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J53" s="12">
         <f>J52+F52</f>
@@ -5219,10 +5237,10 @@
       <c r="B54" s="16"/>
       <c r="C54" s="28"/>
       <c r="D54" s="19" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E54" s="20" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F54" s="21">
         <v>1</v>
@@ -5235,7 +5253,7 @@
         <v>78</v>
       </c>
       <c r="I54" s="24" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="J54" s="12">
         <f t="shared" ref="J54:J81" si="2">F53+J53</f>
@@ -5261,10 +5279,10 @@
       <c r="B55" s="16"/>
       <c r="C55" s="28"/>
       <c r="D55" s="19" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E55" s="20" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F55" s="21">
         <v>1</v>
@@ -5277,7 +5295,7 @@
         <v>79</v>
       </c>
       <c r="I55" s="24" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="J55" s="12">
         <f t="shared" si="2"/>
@@ -5303,10 +5321,10 @@
       <c r="B56" s="16"/>
       <c r="C56" s="28"/>
       <c r="D56" s="19" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E56" s="20" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F56" s="21">
         <v>1</v>
@@ -5319,7 +5337,7 @@
         <v>7A</v>
       </c>
       <c r="I56" s="24" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="J56" s="12">
         <f t="shared" si="2"/>
@@ -5345,10 +5363,10 @@
       <c r="B57" s="16"/>
       <c r="C57" s="28"/>
       <c r="D57" s="19" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E57" s="20" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F57" s="21">
         <v>1</v>
@@ -5361,7 +5379,7 @@
         <v>7B</v>
       </c>
       <c r="I57" s="24" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="J57" s="12">
         <f t="shared" si="2"/>
@@ -5387,10 +5405,10 @@
       <c r="B58" s="16"/>
       <c r="C58" s="28"/>
       <c r="D58" s="19" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E58" s="20" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F58" s="21">
         <v>1</v>
@@ -5403,7 +5421,7 @@
         <v>7C</v>
       </c>
       <c r="I58" s="24" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="J58" s="12">
         <f t="shared" si="2"/>
@@ -5429,10 +5447,10 @@
       <c r="B59" s="16"/>
       <c r="C59" s="28"/>
       <c r="D59" s="19" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E59" s="20" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F59" s="21">
         <v>4</v>
@@ -5445,7 +5463,7 @@
         <v>7D</v>
       </c>
       <c r="I59" s="24" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="J59" s="12">
         <f t="shared" si="2"/>
@@ -5471,10 +5489,10 @@
       <c r="B60" s="16"/>
       <c r="C60" s="28"/>
       <c r="D60" s="19" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E60" s="20" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F60" s="21">
         <v>4</v>
@@ -5487,7 +5505,7 @@
         <v>81</v>
       </c>
       <c r="I60" s="24" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="J60" s="12">
         <f t="shared" si="2"/>
@@ -5513,10 +5531,10 @@
       <c r="B61" s="16"/>
       <c r="C61" s="28"/>
       <c r="D61" s="19" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E61" s="20" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F61" s="21">
         <v>4</v>
@@ -5529,7 +5547,7 @@
         <v>85</v>
       </c>
       <c r="I61" s="24" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="J61" s="12">
         <f t="shared" si="2"/>
@@ -5555,10 +5573,10 @@
       <c r="B62" s="16"/>
       <c r="C62" s="28"/>
       <c r="D62" s="19" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E62" s="20" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F62" s="21">
         <v>1</v>
@@ -5571,7 +5589,7 @@
         <v>89</v>
       </c>
       <c r="I62" s="24" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J62" s="12">
         <f t="shared" si="2"/>
@@ -5597,10 +5615,10 @@
       <c r="B63" s="16"/>
       <c r="C63" s="28"/>
       <c r="D63" s="19" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E63" s="20" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F63" s="21">
         <v>1</v>
@@ -5613,7 +5631,7 @@
         <v>8A</v>
       </c>
       <c r="I63" s="24" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J63" s="12">
         <f t="shared" si="2"/>
@@ -5633,7 +5651,7 @@
       </c>
       <c r="O63" s="35"/>
       <c r="P63" s="36" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64" ht="20.25" spans="1:16">
@@ -5641,10 +5659,10 @@
       <c r="B64" s="16"/>
       <c r="C64" s="28"/>
       <c r="D64" s="19" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F64" s="21">
         <v>1</v>
@@ -5657,7 +5675,7 @@
         <v>8B</v>
       </c>
       <c r="I64" s="24" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="J64" s="12">
         <f t="shared" si="2"/>
@@ -5683,10 +5701,10 @@
       <c r="B65" s="16"/>
       <c r="C65" s="28"/>
       <c r="D65" s="19" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E65" s="20" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F65" s="21">
         <v>1</v>
@@ -5699,7 +5717,7 @@
         <v>8C</v>
       </c>
       <c r="I65" s="24" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="J65" s="12">
         <f t="shared" si="2"/>
@@ -5725,10 +5743,10 @@
       <c r="B66" s="16"/>
       <c r="C66" s="28"/>
       <c r="D66" s="19" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E66" s="20" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F66" s="21">
         <v>1</v>
@@ -5741,7 +5759,7 @@
         <v>8D</v>
       </c>
       <c r="I66" s="24" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="J66" s="12">
         <f t="shared" si="2"/>
@@ -5767,10 +5785,10 @@
       <c r="B67" s="16"/>
       <c r="C67" s="28"/>
       <c r="D67" s="19" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E67" s="20" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F67" s="21">
         <v>1</v>
@@ -5783,7 +5801,7 @@
         <v>8E</v>
       </c>
       <c r="I67" s="24" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="J67" s="12">
         <f t="shared" si="2"/>
@@ -5809,10 +5827,10 @@
       <c r="B68" s="16"/>
       <c r="C68" s="28"/>
       <c r="D68" s="19" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E68" s="20" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F68" s="21">
         <v>2</v>
@@ -5825,7 +5843,7 @@
         <v>8F</v>
       </c>
       <c r="I68" s="24" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J68" s="12">
         <f t="shared" si="2"/>
@@ -5851,10 +5869,10 @@
       <c r="B69" s="16"/>
       <c r="C69" s="28"/>
       <c r="D69" s="19" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E69" s="20" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F69" s="21">
         <v>1</v>
@@ -5867,7 +5885,7 @@
         <v>91</v>
       </c>
       <c r="I69" s="24" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="J69" s="12">
         <f t="shared" si="2"/>
@@ -5893,10 +5911,10 @@
       <c r="B70" s="16"/>
       <c r="C70" s="28"/>
       <c r="D70" s="19" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F70" s="21">
         <v>1</v>
@@ -5909,7 +5927,7 @@
         <v>92</v>
       </c>
       <c r="I70" s="19" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="J70" s="12">
         <f t="shared" si="2"/>
@@ -5935,10 +5953,10 @@
       <c r="B71" s="16"/>
       <c r="C71" s="28"/>
       <c r="D71" s="19" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F71" s="21">
         <v>1</v>
@@ -5951,7 +5969,7 @@
         <v>93</v>
       </c>
       <c r="I71" s="19" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="J71" s="12">
         <f t="shared" si="2"/>
@@ -5977,10 +5995,10 @@
       <c r="B72" s="16"/>
       <c r="C72" s="28"/>
       <c r="D72" s="19" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F72" s="21">
         <v>1</v>
@@ -5993,7 +6011,7 @@
         <v>94</v>
       </c>
       <c r="I72" s="19" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="J72" s="12">
         <f t="shared" si="2"/>
@@ -6019,10 +6037,10 @@
       <c r="B73" s="16"/>
       <c r="C73" s="28"/>
       <c r="D73" s="19" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E73" s="20" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F73" s="21">
         <v>1</v>
@@ -6035,7 +6053,7 @@
         <v>95</v>
       </c>
       <c r="I73" s="19" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="J73" s="12">
         <f t="shared" si="2"/>
@@ -6061,10 +6079,10 @@
       <c r="B74" s="16"/>
       <c r="C74" s="28"/>
       <c r="D74" s="19" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E74" s="20" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F74" s="21">
         <v>1</v>
@@ -6077,7 +6095,7 @@
         <v>96</v>
       </c>
       <c r="I74" s="19" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="J74" s="12">
         <f t="shared" si="2"/>
@@ -6103,10 +6121,10 @@
       <c r="B75" s="16"/>
       <c r="C75" s="28"/>
       <c r="D75" s="19" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E75" s="20" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F75" s="21">
         <v>1</v>
@@ -6119,7 +6137,7 @@
         <v>97</v>
       </c>
       <c r="I75" s="19" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="J75" s="12">
         <f t="shared" si="2"/>
@@ -6145,10 +6163,10 @@
       <c r="B76" s="16"/>
       <c r="C76" s="28"/>
       <c r="D76" s="19" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F76" s="21">
         <v>1</v>
@@ -6161,7 +6179,7 @@
         <v>98</v>
       </c>
       <c r="I76" s="19" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="J76" s="12">
         <f t="shared" si="2"/>
@@ -6187,10 +6205,10 @@
       <c r="B77" s="16"/>
       <c r="C77" s="28"/>
       <c r="D77" s="19" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E77" s="20" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F77" s="21">
         <v>1</v>
@@ -6203,7 +6221,7 @@
         <v>99</v>
       </c>
       <c r="I77" s="19" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="J77" s="12">
         <f t="shared" si="2"/>
@@ -6229,10 +6247,10 @@
       <c r="B78" s="16"/>
       <c r="C78" s="28"/>
       <c r="D78" s="19" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F78" s="21">
         <v>1</v>
@@ -6245,7 +6263,7 @@
         <v>9A</v>
       </c>
       <c r="I78" s="19" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J78" s="12">
         <f t="shared" si="2"/>
@@ -6271,10 +6289,10 @@
       <c r="B79" s="16"/>
       <c r="C79" s="28"/>
       <c r="D79" s="19" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E79" s="20" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="F79" s="21">
         <v>1</v>
@@ -6287,7 +6305,7 @@
         <v>9B</v>
       </c>
       <c r="I79" s="19" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="J79" s="12">
         <f t="shared" si="2"/>
@@ -6313,10 +6331,10 @@
       <c r="B80" s="16"/>
       <c r="C80" s="28"/>
       <c r="D80" s="37" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E80" s="38" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F80" s="21">
         <v>1</v>
@@ -6329,7 +6347,7 @@
         <v>9C</v>
       </c>
       <c r="I80" s="37" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="J80" s="12">
         <f t="shared" si="2"/>
@@ -6355,10 +6373,10 @@
       <c r="B81" s="16"/>
       <c r="C81" s="28"/>
       <c r="D81" s="25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E81" s="25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F81" s="26">
         <v>8</v>
@@ -6393,17 +6411,17 @@
     <row r="82" ht="20.25" spans="1:16">
       <c r="A82" s="16"/>
       <c r="B82" s="17" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C82" s="18">
         <f>SUM(F113,J113)-J82</f>
         <v>53</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F82" s="21">
         <v>1</v>
@@ -6416,7 +6434,7 @@
         <v>A5</v>
       </c>
       <c r="I82" s="24" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="J82" s="12">
         <f t="shared" ref="J81:J123" si="5">F81+J81</f>
@@ -6442,10 +6460,10 @@
       <c r="B83" s="17"/>
       <c r="C83" s="18"/>
       <c r="D83" s="19" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E83" s="20" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F83" s="21">
         <v>1</v>
@@ -6458,7 +6476,7 @@
         <v>A6</v>
       </c>
       <c r="I83" s="46" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="J83" s="12">
         <f t="shared" si="5"/>
@@ -6484,10 +6502,10 @@
       <c r="B84" s="17"/>
       <c r="C84" s="18"/>
       <c r="D84" s="19" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E84" s="20" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F84" s="21">
         <v>4</v>
@@ -6500,7 +6518,7 @@
         <v>A7</v>
       </c>
       <c r="I84" s="24" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="J84" s="12">
         <f t="shared" si="5"/>
@@ -6526,10 +6544,10 @@
       <c r="B85" s="17"/>
       <c r="C85" s="18"/>
       <c r="D85" s="19" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E85" s="20" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F85" s="21">
         <v>1</v>
@@ -6542,7 +6560,7 @@
         <v>AB</v>
       </c>
       <c r="I85" s="24" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="J85" s="12">
         <f t="shared" si="5"/>
@@ -6568,10 +6586,10 @@
       <c r="B86" s="17"/>
       <c r="C86" s="18"/>
       <c r="D86" s="19" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E86" s="20" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="F86" s="21">
         <v>1</v>
@@ -6584,7 +6602,7 @@
         <v>AC</v>
       </c>
       <c r="I86" s="24" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="J86" s="12">
         <f t="shared" si="5"/>
@@ -6610,10 +6628,10 @@
       <c r="B87" s="17"/>
       <c r="C87" s="18"/>
       <c r="D87" s="19" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E87" s="20" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F87" s="21">
         <v>1</v>
@@ -6626,7 +6644,7 @@
         <v>AD</v>
       </c>
       <c r="I87" s="46" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="J87" s="12">
         <f t="shared" si="5"/>
@@ -6652,10 +6670,10 @@
       <c r="B88" s="17"/>
       <c r="C88" s="18"/>
       <c r="D88" s="19" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E88" s="20" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F88" s="21">
         <v>1</v>
@@ -6668,7 +6686,7 @@
         <v>AE</v>
       </c>
       <c r="I88" s="46" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="J88" s="12">
         <f t="shared" si="5"/>
@@ -6694,10 +6712,10 @@
       <c r="B89" s="17"/>
       <c r="C89" s="18"/>
       <c r="D89" s="19" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F89" s="21">
         <v>4</v>
@@ -6710,7 +6728,7 @@
         <v>AF</v>
       </c>
       <c r="I89" s="24" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="J89" s="12">
         <f t="shared" si="5"/>
@@ -6736,10 +6754,10 @@
       <c r="B90" s="17"/>
       <c r="C90" s="18"/>
       <c r="D90" s="19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E90" s="20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F90" s="21">
         <v>1</v>
@@ -6752,7 +6770,7 @@
         <v>B3</v>
       </c>
       <c r="I90" s="24" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="J90" s="12">
         <f t="shared" si="5"/>
@@ -6778,10 +6796,10 @@
       <c r="B91" s="17"/>
       <c r="C91" s="18"/>
       <c r="D91" s="19" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E91" s="20" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="F91" s="21">
         <v>1</v>
@@ -6794,7 +6812,7 @@
         <v>B4</v>
       </c>
       <c r="I91" s="24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="J91" s="12">
         <f t="shared" si="5"/>
@@ -6820,10 +6838,10 @@
       <c r="B92" s="17"/>
       <c r="C92" s="18"/>
       <c r="D92" s="19" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="F92" s="21">
         <v>1</v>
@@ -6836,7 +6854,7 @@
         <v>B5</v>
       </c>
       <c r="I92" s="24" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="J92" s="12">
         <f t="shared" si="5"/>
@@ -6862,10 +6880,10 @@
       <c r="B93" s="17"/>
       <c r="C93" s="18"/>
       <c r="D93" s="19" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E93" s="20" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F93" s="21">
         <v>1</v>
@@ -6878,7 +6896,7 @@
         <v>B6</v>
       </c>
       <c r="I93" s="24" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="J93" s="12">
         <f t="shared" si="5"/>
@@ -6904,10 +6922,10 @@
       <c r="B94" s="17"/>
       <c r="C94" s="18"/>
       <c r="D94" s="19" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F94" s="21">
         <v>1</v>
@@ -6920,7 +6938,7 @@
         <v>B7</v>
       </c>
       <c r="I94" s="24" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="J94" s="12">
         <f t="shared" si="5"/>
@@ -6946,10 +6964,10 @@
       <c r="B95" s="17"/>
       <c r="C95" s="18"/>
       <c r="D95" s="19" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E95" s="20" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F95" s="21">
         <v>1</v>
@@ -6962,7 +6980,7 @@
         <v>B8</v>
       </c>
       <c r="I95" s="24" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="J95" s="12">
         <f t="shared" si="5"/>
@@ -6988,10 +7006,10 @@
       <c r="B96" s="17"/>
       <c r="C96" s="18"/>
       <c r="D96" s="19" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E96" s="20" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F96" s="21">
         <v>1</v>
@@ -7004,7 +7022,7 @@
         <v>B9</v>
       </c>
       <c r="I96" s="24" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="J96" s="12">
         <f t="shared" si="5"/>
@@ -7030,10 +7048,10 @@
       <c r="B97" s="17"/>
       <c r="C97" s="18"/>
       <c r="D97" s="19" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E97" s="20" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="F97" s="21">
         <v>4</v>
@@ -7046,7 +7064,7 @@
         <v>BA</v>
       </c>
       <c r="I97" s="24" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="J97" s="12">
         <f t="shared" si="5"/>
@@ -7072,10 +7090,10 @@
       <c r="B98" s="17"/>
       <c r="C98" s="18"/>
       <c r="D98" s="19" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F98" s="21">
         <v>1</v>
@@ -7088,7 +7106,7 @@
         <v>BE</v>
       </c>
       <c r="I98" s="24" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="J98" s="12">
         <f t="shared" si="5"/>
@@ -7114,10 +7132,10 @@
       <c r="B99" s="17"/>
       <c r="C99" s="18"/>
       <c r="D99" s="19" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="E99" s="20" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F99" s="21">
         <v>1</v>
@@ -7130,7 +7148,7 @@
         <v>BF</v>
       </c>
       <c r="I99" s="24" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="J99" s="12">
         <f t="shared" si="5"/>
@@ -7156,10 +7174,10 @@
       <c r="B100" s="17"/>
       <c r="C100" s="18"/>
       <c r="D100" s="19" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E100" s="20" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F100" s="21">
         <v>1</v>
@@ -7172,7 +7190,7 @@
         <v>C0</v>
       </c>
       <c r="I100" s="24" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="J100" s="12">
         <f t="shared" si="5"/>
@@ -7198,10 +7216,10 @@
       <c r="B101" s="17"/>
       <c r="C101" s="18"/>
       <c r="D101" s="19" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F101" s="21">
         <v>1</v>
@@ -7214,7 +7232,7 @@
         <v>C1</v>
       </c>
       <c r="I101" s="24" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="J101" s="12">
         <f t="shared" si="5"/>
@@ -7240,10 +7258,10 @@
       <c r="B102" s="17"/>
       <c r="C102" s="18"/>
       <c r="D102" s="19" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E102" s="20" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="F102" s="21">
         <v>1</v>
@@ -7256,7 +7274,7 @@
         <v>C2</v>
       </c>
       <c r="I102" s="24" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="J102" s="12">
         <f t="shared" si="5"/>
@@ -7282,10 +7300,10 @@
       <c r="B103" s="17"/>
       <c r="C103" s="18"/>
       <c r="D103" s="37" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="E103" s="38" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="F103" s="21">
         <v>1</v>
@@ -7298,7 +7316,7 @@
         <v>C3</v>
       </c>
       <c r="I103" s="51" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="J103" s="12">
         <f t="shared" si="5"/>
@@ -7324,10 +7342,10 @@
       <c r="B104" s="17"/>
       <c r="C104" s="18"/>
       <c r="D104" s="37" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E104" s="38" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F104" s="21">
         <v>1</v>
@@ -7340,7 +7358,7 @@
         <v>C4</v>
       </c>
       <c r="I104" s="51" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J104" s="12">
         <f t="shared" si="5"/>
@@ -7366,10 +7384,10 @@
       <c r="B105" s="17"/>
       <c r="C105" s="18"/>
       <c r="D105" s="37" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E105" s="38" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F105" s="21">
         <v>1</v>
@@ -7382,7 +7400,7 @@
         <v>C5</v>
       </c>
       <c r="I105" s="51" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="J105" s="12">
         <f t="shared" si="5"/>
@@ -7408,10 +7426,10 @@
       <c r="B106" s="17"/>
       <c r="C106" s="18"/>
       <c r="D106" s="37" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E106" s="38" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="F106" s="21">
         <v>1</v>
@@ -7424,7 +7442,7 @@
         <v>C6</v>
       </c>
       <c r="I106" s="51" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="J106" s="12">
         <f t="shared" si="5"/>
@@ -7450,10 +7468,10 @@
       <c r="B107" s="17"/>
       <c r="C107" s="18"/>
       <c r="D107" s="37" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E107" s="38" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="F107" s="21">
         <v>1</v>
@@ -7466,7 +7484,7 @@
         <v>C7</v>
       </c>
       <c r="I107" s="51" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="J107" s="12">
         <f t="shared" si="5"/>
@@ -7492,10 +7510,10 @@
       <c r="B108" s="17"/>
       <c r="C108" s="18"/>
       <c r="D108" s="37" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E108" s="38" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="F108" s="21">
         <v>4</v>
@@ -7508,7 +7526,7 @@
         <v>C8</v>
       </c>
       <c r="I108" s="51" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="J108" s="12">
         <f t="shared" si="5"/>
@@ -7534,10 +7552,10 @@
       <c r="B109" s="17"/>
       <c r="C109" s="18"/>
       <c r="D109" s="37" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E109" s="38" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F109" s="21">
         <v>1</v>
@@ -7550,7 +7568,7 @@
         <v>CC</v>
       </c>
       <c r="I109" s="51" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="J109" s="12">
         <f t="shared" si="5"/>
@@ -7576,10 +7594,10 @@
       <c r="B110" s="17"/>
       <c r="C110" s="18"/>
       <c r="D110" s="37" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E110" s="38" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F110" s="21">
         <v>1</v>
@@ -7592,7 +7610,7 @@
         <v>CD</v>
       </c>
       <c r="I110" s="51" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="J110" s="12">
         <f t="shared" si="5"/>
@@ -7618,10 +7636,10 @@
       <c r="B111" s="17"/>
       <c r="C111" s="18"/>
       <c r="D111" s="37" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E111" s="38" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F111" s="21">
         <v>2</v>
@@ -7634,7 +7652,7 @@
         <v>CE</v>
       </c>
       <c r="I111" s="51" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="J111" s="12">
         <f t="shared" si="5"/>
@@ -7660,10 +7678,10 @@
       <c r="B112" s="17"/>
       <c r="C112" s="18"/>
       <c r="D112" s="37" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E112" s="38" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F112" s="21">
         <v>1</v>
@@ -7676,7 +7694,7 @@
         <v>D0</v>
       </c>
       <c r="I112" s="51" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J112" s="12">
         <f t="shared" si="5"/>
@@ -7689,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="M112" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N112" s="12" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="O112" s="30" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="P112" s="31"/>
     </row>
@@ -7704,10 +7722,10 @@
       <c r="B113" s="17"/>
       <c r="C113" s="18"/>
       <c r="D113" s="25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E113" s="25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F113" s="26">
         <v>9</v>
@@ -7742,17 +7760,17 @@
     <row r="114" ht="20.25" spans="1:16">
       <c r="A114" s="16"/>
       <c r="B114" s="17" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C114" s="18">
         <f>SUM(F126,J126)-J114</f>
         <v>25</v>
       </c>
       <c r="D114" s="19" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F114" s="21">
         <v>1</v>
@@ -7765,7 +7783,7 @@
         <v>DA</v>
       </c>
       <c r="I114" s="24" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="J114" s="12">
         <f t="shared" si="5"/>
@@ -7791,10 +7809,10 @@
       <c r="B115" s="17"/>
       <c r="C115" s="18"/>
       <c r="D115" s="19" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E115" s="20" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F115" s="21">
         <v>1</v>
@@ -7807,7 +7825,7 @@
         <v>DB</v>
       </c>
       <c r="I115" s="24" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J115" s="12">
         <f t="shared" si="5"/>
@@ -7833,10 +7851,10 @@
       <c r="B116" s="17"/>
       <c r="C116" s="18"/>
       <c r="D116" s="19" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E116" s="20" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="F116" s="21">
         <v>2</v>
@@ -7849,7 +7867,7 @@
         <v>DC</v>
       </c>
       <c r="I116" s="19" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="J116" s="12">
         <f t="shared" si="5"/>
@@ -7875,10 +7893,10 @@
       <c r="B117" s="17"/>
       <c r="C117" s="18"/>
       <c r="D117" s="19" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E117" s="20" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F117" s="21">
         <v>2</v>
@@ -7891,7 +7909,7 @@
         <v>DE</v>
       </c>
       <c r="I117" s="19" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="J117" s="12">
         <f t="shared" si="5"/>
@@ -7917,10 +7935,10 @@
       <c r="B118" s="17"/>
       <c r="C118" s="18"/>
       <c r="D118" s="19" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E118" s="20" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F118" s="21">
         <v>2</v>
@@ -7933,7 +7951,7 @@
         <v>E0</v>
       </c>
       <c r="I118" s="19" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="J118" s="12">
         <f t="shared" si="5"/>
@@ -7959,10 +7977,10 @@
       <c r="B119" s="17"/>
       <c r="C119" s="18"/>
       <c r="D119" s="19" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E119" s="20" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F119" s="21">
         <v>1</v>
@@ -7975,7 +7993,7 @@
         <v>E2</v>
       </c>
       <c r="I119" s="19" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="J119" s="12">
         <f t="shared" si="5"/>
@@ -8001,10 +8019,10 @@
       <c r="B120" s="17"/>
       <c r="C120" s="18"/>
       <c r="D120" s="19" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E120" s="20" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F120" s="21">
         <v>1</v>
@@ -8017,7 +8035,7 @@
         <v>E3</v>
       </c>
       <c r="I120" s="19" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="J120" s="12">
         <f t="shared" si="5"/>
@@ -8043,10 +8061,10 @@
       <c r="B121" s="17"/>
       <c r="C121" s="18"/>
       <c r="D121" s="19" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E121" s="20" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F121" s="21">
         <v>1</v>
@@ -8059,7 +8077,7 @@
         <v>E4</v>
       </c>
       <c r="I121" s="19" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="J121" s="12">
         <f t="shared" si="5"/>
@@ -8085,10 +8103,10 @@
       <c r="B122" s="17"/>
       <c r="C122" s="18"/>
       <c r="D122" s="19" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E122" s="20" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F122" s="21">
         <v>1</v>
@@ -8101,7 +8119,7 @@
         <v>E5</v>
       </c>
       <c r="I122" s="19" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="J122" s="12">
         <f t="shared" si="5"/>
@@ -8127,10 +8145,10 @@
       <c r="B123" s="41"/>
       <c r="C123" s="42"/>
       <c r="D123" s="19" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E123" s="20" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F123" s="21">
         <v>1</v>
@@ -8143,7 +8161,7 @@
         <v>E6</v>
       </c>
       <c r="I123" s="19" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="J123" s="12">
         <f t="shared" si="5"/>
@@ -8168,10 +8186,10 @@
       <c r="B124" s="41"/>
       <c r="C124" s="42"/>
       <c r="D124" s="19" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E124" s="20" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F124" s="21">
         <v>1</v>
@@ -8184,7 +8202,7 @@
         <v>E7</v>
       </c>
       <c r="I124" s="19" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="J124" s="12">
         <f t="shared" ref="J124:J143" si="7">F123+J123</f>
@@ -8209,10 +8227,10 @@
       <c r="B125" s="41"/>
       <c r="C125" s="42"/>
       <c r="D125" s="19" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E125" s="20" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F125" s="21">
         <v>1</v>
@@ -8225,7 +8243,7 @@
         <v>E8</v>
       </c>
       <c r="I125" s="19" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="J125" s="12">
         <f t="shared" si="7"/>
@@ -8250,10 +8268,10 @@
       <c r="B126" s="17"/>
       <c r="C126" s="18"/>
       <c r="D126" s="25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E126" s="25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F126" s="26">
         <v>10</v>
@@ -8288,17 +8306,17 @@
     <row r="127" ht="20.25" spans="1:16">
       <c r="A127" s="16"/>
       <c r="B127" s="43" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C127" s="44">
         <f>SUM(F132,J132)-J127</f>
         <v>20</v>
       </c>
       <c r="D127" s="19" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E127" s="20" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F127" s="21">
         <v>8</v>
@@ -8311,14 +8329,14 @@
         <v>F3</v>
       </c>
       <c r="I127" s="19" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="J127" s="12">
         <f t="shared" si="7"/>
         <v>243</v>
       </c>
       <c r="K127" s="12" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="L127" s="12">
         <v>2</v>
@@ -8337,10 +8355,10 @@
       <c r="B128" s="16"/>
       <c r="C128" s="45"/>
       <c r="D128" s="19" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E128" s="20" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F128" s="21">
         <v>8</v>
@@ -8353,14 +8371,14 @@
         <v>FB</v>
       </c>
       <c r="I128" s="19" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="J128" s="12">
         <f t="shared" si="7"/>
         <v>251</v>
       </c>
       <c r="K128" s="12" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="L128" s="12">
         <v>2</v>
@@ -8379,10 +8397,10 @@
       <c r="B129" s="16"/>
       <c r="C129" s="45"/>
       <c r="D129" s="19" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E129" s="20" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F129" s="21">
         <v>1</v>
@@ -8395,7 +8413,7 @@
         <v>103</v>
       </c>
       <c r="I129" s="24" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="J129" s="12">
         <f t="shared" si="7"/>
@@ -8421,10 +8439,10 @@
       <c r="B130" s="16"/>
       <c r="C130" s="45"/>
       <c r="D130" s="19" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E130" s="20" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F130" s="21">
         <v>1</v>
@@ -8437,7 +8455,7 @@
         <v>104</v>
       </c>
       <c r="I130" s="24" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="J130" s="12">
         <f t="shared" si="7"/>
@@ -8456,7 +8474,7 @@
         <v>13</v>
       </c>
       <c r="O130" s="32" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="P130" s="31"/>
     </row>
@@ -8465,10 +8483,10 @@
       <c r="B131" s="16"/>
       <c r="C131" s="45"/>
       <c r="D131" s="19" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E131" s="20" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F131" s="21">
         <v>1</v>
@@ -8481,7 +8499,7 @@
         <v>105</v>
       </c>
       <c r="I131" s="24" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="J131" s="12">
         <f t="shared" si="7"/>
@@ -8500,7 +8518,7 @@
         <v>13</v>
       </c>
       <c r="O131" s="32" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="P131" s="31"/>
     </row>
@@ -8509,7 +8527,7 @@
       <c r="B132" s="53"/>
       <c r="C132" s="54"/>
       <c r="D132" s="55" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E132" s="20"/>
       <c r="F132" s="21">
@@ -8544,20 +8562,20 @@
     </row>
     <row r="133" ht="20.25" spans="1:16">
       <c r="A133" s="17" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B133" s="43" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C133" s="44">
         <f>SUM(F143,J143)-J133</f>
         <v>66</v>
       </c>
       <c r="D133" s="19" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E133" s="20" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F133" s="21">
         <v>4</v>
@@ -8570,7 +8588,7 @@
         <v>107</v>
       </c>
       <c r="I133" s="24" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="J133" s="12">
         <f t="shared" si="7"/>
@@ -8596,10 +8614,10 @@
       <c r="B134" s="16"/>
       <c r="C134" s="45"/>
       <c r="D134" s="19" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E134" s="20" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F134" s="21">
         <v>4</v>
@@ -8612,7 +8630,7 @@
         <v>10B</v>
       </c>
       <c r="I134" s="24" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="J134" s="12">
         <f t="shared" si="7"/>
@@ -8638,10 +8656,10 @@
       <c r="B135" s="16"/>
       <c r="C135" s="45"/>
       <c r="D135" s="19" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E135" s="20" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F135" s="21">
         <v>1</v>
@@ -8654,7 +8672,7 @@
         <v>10F</v>
       </c>
       <c r="I135" s="24" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="J135" s="12">
         <f t="shared" si="7"/>
@@ -8680,10 +8698,10 @@
       <c r="B136" s="16"/>
       <c r="C136" s="45"/>
       <c r="D136" s="19" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="E136" s="20" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F136" s="21">
         <v>1</v>
@@ -8696,7 +8714,7 @@
         <v>110</v>
       </c>
       <c r="I136" s="24" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="J136" s="12">
         <f t="shared" si="7"/>
@@ -8715,7 +8733,7 @@
         <v>13</v>
       </c>
       <c r="O136" s="32" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="P136" s="31"/>
     </row>
@@ -8724,10 +8742,10 @@
       <c r="B137" s="16"/>
       <c r="C137" s="45"/>
       <c r="D137" s="56" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E137" s="20" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F137" s="21">
         <v>4</v>
@@ -8740,7 +8758,7 @@
         <v>111</v>
       </c>
       <c r="I137" s="24" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="J137" s="12">
         <f t="shared" si="7"/>
@@ -8766,10 +8784,10 @@
       <c r="B138" s="16"/>
       <c r="C138" s="45"/>
       <c r="D138" s="56" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E138" s="20" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F138" s="21">
         <v>4</v>
@@ -8782,7 +8800,7 @@
         <v>115</v>
       </c>
       <c r="I138" s="24" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="J138" s="12">
         <f t="shared" si="7"/>
@@ -8808,10 +8826,10 @@
       <c r="B139" s="16"/>
       <c r="C139" s="45"/>
       <c r="D139" s="19" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E139" s="20" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F139" s="21">
         <v>1</v>
@@ -8824,7 +8842,7 @@
         <v>119</v>
       </c>
       <c r="I139" s="24" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="J139" s="12">
         <f t="shared" si="7"/>
@@ -8843,7 +8861,7 @@
         <v>13</v>
       </c>
       <c r="O139" s="68" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="P139" s="31"/>
     </row>
@@ -8852,10 +8870,10 @@
       <c r="B140" s="16"/>
       <c r="C140" s="45"/>
       <c r="D140" s="56" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E140" s="20" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F140" s="21">
         <v>8</v>
@@ -8868,14 +8886,14 @@
         <v>11A</v>
       </c>
       <c r="I140" s="24" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="J140" s="12">
         <f t="shared" si="7"/>
         <v>282</v>
       </c>
       <c r="K140" s="12" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="L140" s="12">
         <v>2</v>
@@ -8894,10 +8912,10 @@
       <c r="B141" s="16"/>
       <c r="C141" s="45"/>
       <c r="D141" s="56" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E141" s="20" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F141" s="21">
         <v>8</v>
@@ -8910,14 +8928,14 @@
         <v>122</v>
       </c>
       <c r="I141" s="24" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="J141" s="12">
         <f t="shared" si="7"/>
         <v>290</v>
       </c>
       <c r="K141" s="12" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="L141" s="12">
         <v>2</v>
@@ -8936,10 +8954,10 @@
       <c r="B142" s="16"/>
       <c r="C142" s="45"/>
       <c r="D142" s="56" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E142" s="20" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F142" s="21">
         <v>1</v>
@@ -8969,7 +8987,7 @@
         <v>13</v>
       </c>
       <c r="O142" s="32" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="P142" s="31"/>
     </row>
@@ -8978,10 +8996,10 @@
       <c r="B143" s="53"/>
       <c r="C143" s="54"/>
       <c r="D143" s="57" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E143" s="25" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F143" s="26">
         <v>30</v>
@@ -9016,14 +9034,14 @@
     <row r="144" s="3" customFormat="1" ht="20.25" spans="1:16">
       <c r="A144" s="17"/>
       <c r="B144" s="58" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C144" s="59"/>
       <c r="D144" s="60" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E144" s="38" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F144" s="21">
         <v>1</v>
@@ -9036,7 +9054,7 @@
         <v>149</v>
       </c>
       <c r="I144" s="51" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J144" s="12">
         <f t="shared" ref="J143:J151" si="9">F143+J143</f>
@@ -9055,10 +9073,10 @@
         <v>13</v>
       </c>
       <c r="O144" s="69" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="P144" s="3" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="145" s="3" customFormat="1" ht="20.25" spans="1:15">
@@ -9066,10 +9084,10 @@
       <c r="B145" s="58"/>
       <c r="C145" s="61"/>
       <c r="D145" s="60" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E145" s="38" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F145" s="21">
         <v>2</v>
@@ -9082,7 +9100,7 @@
         <v>14A</v>
       </c>
       <c r="I145" s="51" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="J145" s="12">
         <f t="shared" si="9"/>
@@ -9107,10 +9125,10 @@
       <c r="B146" s="62"/>
       <c r="C146" s="45"/>
       <c r="D146" s="60" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E146" s="38" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F146" s="21">
         <v>1</v>
@@ -9123,7 +9141,7 @@
         <v>14C</v>
       </c>
       <c r="I146" s="37" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="J146" s="12">
         <f t="shared" si="9"/>
@@ -9142,10 +9160,10 @@
         <v>13</v>
       </c>
       <c r="O146" s="30" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="P146" s="70" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="147" customFormat="1" ht="20.25" spans="1:16">
@@ -9153,10 +9171,10 @@
       <c r="B147" s="62"/>
       <c r="C147" s="45"/>
       <c r="D147" s="60" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E147" s="20" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F147" s="21">
         <v>1</v>
@@ -9169,7 +9187,7 @@
         <v>14D</v>
       </c>
       <c r="I147" s="37" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="J147" s="12">
         <f t="shared" si="9"/>
@@ -9195,10 +9213,10 @@
       <c r="B148" s="62"/>
       <c r="C148" s="45"/>
       <c r="D148" s="60" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="E148" s="20" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F148" s="21">
         <v>4</v>
@@ -9211,14 +9229,14 @@
         <v>14E</v>
       </c>
       <c r="I148" s="37" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="J148" s="12">
         <f t="shared" si="9"/>
         <v>334</v>
       </c>
       <c r="K148" s="12" t="s">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="L148" s="12">
         <v>2</v>
@@ -9227,10 +9245,10 @@
         <v>1</v>
       </c>
       <c r="N148" s="12" t="s">
-        <v>13</v>
+        <v>451</v>
       </c>
       <c r="O148" s="30" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="P148" s="70"/>
     </row>
@@ -9239,10 +9257,10 @@
       <c r="B149" s="62"/>
       <c r="C149" s="45"/>
       <c r="D149" s="60" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E149" s="20" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="F149" s="21">
         <v>4</v>
@@ -9255,14 +9273,14 @@
         <v>152</v>
       </c>
       <c r="I149" s="37" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="J149" s="12">
         <f t="shared" si="9"/>
         <v>338</v>
       </c>
       <c r="K149" s="12" t="s">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="L149" s="12">
         <v>2</v>
@@ -9271,10 +9289,10 @@
         <v>1</v>
       </c>
       <c r="N149" s="12" t="s">
-        <v>13</v>
+        <v>456</v>
       </c>
       <c r="O149" s="30" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="P149" s="70"/>
     </row>
@@ -9283,10 +9301,10 @@
       <c r="B150" s="62"/>
       <c r="C150" s="45"/>
       <c r="D150" s="60" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="E150" s="20" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F150" s="21">
         <v>1</v>
@@ -9299,7 +9317,7 @@
         <v>156</v>
       </c>
       <c r="I150" s="37" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="J150" s="12">
         <f t="shared" si="9"/>
@@ -9325,10 +9343,10 @@
       <c r="B151" s="58"/>
       <c r="C151" s="63"/>
       <c r="D151" s="60" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E151" s="20" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="F151" s="21">
         <v>1</v>
@@ -9341,7 +9359,7 @@
         <v>157</v>
       </c>
       <c r="I151" s="37" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="J151" s="12">
         <f t="shared" si="9"/>
@@ -9367,10 +9385,10 @@
       <c r="B152" s="62"/>
       <c r="C152" s="45"/>
       <c r="D152" s="60" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="E152" s="20" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="F152" s="21">
         <v>2</v>
@@ -9383,7 +9401,7 @@
         <v>158</v>
       </c>
       <c r="I152" s="37" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="J152" s="12">
         <f t="shared" ref="J152:J167" si="12">F151+J151</f>
@@ -9409,10 +9427,10 @@
       <c r="B153" s="62"/>
       <c r="C153" s="45"/>
       <c r="D153" s="60" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="E153" s="20" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="F153" s="21">
         <v>1</v>
@@ -9425,7 +9443,7 @@
         <v>15A</v>
       </c>
       <c r="I153" s="37" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="J153" s="12">
         <f t="shared" si="12"/>
@@ -9451,10 +9469,10 @@
       <c r="B154" s="62"/>
       <c r="C154" s="45"/>
       <c r="D154" s="60" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="E154" s="20" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="F154" s="21">
         <v>1</v>
@@ -9467,7 +9485,7 @@
         <v>15B</v>
       </c>
       <c r="I154" s="37" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="J154" s="12">
         <f t="shared" si="12"/>
@@ -9493,10 +9511,10 @@
       <c r="B155" s="62"/>
       <c r="C155" s="45"/>
       <c r="D155" s="60" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E155" s="20" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F155" s="21">
         <v>2</v>
@@ -9509,7 +9527,7 @@
         <v>15C</v>
       </c>
       <c r="I155" s="37" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="J155" s="12">
         <f t="shared" si="12"/>
@@ -9535,10 +9553,10 @@
       <c r="B156" s="62"/>
       <c r="C156" s="45"/>
       <c r="D156" s="60" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="E156" s="20" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F156" s="21">
         <v>1</v>
@@ -9551,7 +9569,7 @@
         <v>15E</v>
       </c>
       <c r="I156" s="37" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="J156" s="12">
         <f t="shared" si="12"/>
@@ -9577,10 +9595,10 @@
       <c r="B157" s="62"/>
       <c r="C157" s="45"/>
       <c r="D157" s="60" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="E157" s="20" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="F157" s="21">
         <v>1</v>
@@ -9593,7 +9611,7 @@
         <v>15F</v>
       </c>
       <c r="I157" s="37" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="J157" s="12">
         <f t="shared" si="12"/>
@@ -9619,10 +9637,10 @@
       <c r="B158" s="62"/>
       <c r="C158" s="45"/>
       <c r="D158" s="60" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="E158" s="20" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="F158" s="21">
         <v>2</v>
@@ -9635,7 +9653,7 @@
         <v>160</v>
       </c>
       <c r="I158" s="37" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="J158" s="12">
         <f t="shared" si="12"/>
@@ -9661,10 +9679,10 @@
       <c r="B159" s="62"/>
       <c r="C159" s="45"/>
       <c r="D159" s="60" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E159" s="20" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="F159" s="21">
         <v>1</v>
@@ -9677,7 +9695,7 @@
         <v>162</v>
       </c>
       <c r="I159" s="37" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="J159" s="12">
         <f t="shared" si="12"/>
@@ -9703,10 +9721,10 @@
       <c r="B160" s="62"/>
       <c r="C160" s="45"/>
       <c r="D160" s="60" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="E160" s="20" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="F160" s="21">
         <v>1</v>
@@ -9719,7 +9737,7 @@
         <v>163</v>
       </c>
       <c r="I160" s="37" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="J160" s="12">
         <f t="shared" si="12"/>
@@ -9745,10 +9763,10 @@
       <c r="B161" s="62"/>
       <c r="C161" s="45"/>
       <c r="D161" s="60" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="E161" s="20" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="F161" s="21">
         <v>2</v>
@@ -9761,7 +9779,7 @@
         <v>164</v>
       </c>
       <c r="I161" s="37" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="J161" s="12">
         <f t="shared" si="12"/>
@@ -9787,10 +9805,10 @@
       <c r="B162" s="62"/>
       <c r="C162" s="45"/>
       <c r="D162" s="60" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="E162" s="20" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="F162" s="21">
         <v>1</v>
@@ -9803,7 +9821,7 @@
         <v>166</v>
       </c>
       <c r="I162" s="37" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="J162" s="12">
         <f t="shared" si="12"/>
@@ -9829,10 +9847,10 @@
       <c r="B163" s="62"/>
       <c r="C163" s="45"/>
       <c r="D163" s="60" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E163" s="20" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="F163" s="21">
         <v>1</v>
@@ -9845,7 +9863,7 @@
         <v>167</v>
       </c>
       <c r="I163" s="37" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="J163" s="12">
         <f t="shared" si="12"/>
@@ -9871,10 +9889,10 @@
       <c r="B164" s="62"/>
       <c r="C164" s="45"/>
       <c r="D164" s="60" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="E164" s="20" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="F164" s="21">
         <v>4</v>
@@ -9887,7 +9905,7 @@
         <v>168</v>
       </c>
       <c r="I164" s="37" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="J164" s="12">
         <f t="shared" si="12"/>
@@ -9913,10 +9931,10 @@
       <c r="B165" s="62"/>
       <c r="C165" s="45"/>
       <c r="D165" s="60" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="E165" s="20" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="F165" s="21">
         <v>4</v>
@@ -9929,7 +9947,7 @@
         <v>16C</v>
       </c>
       <c r="I165" s="37" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="J165" s="12">
         <f t="shared" si="12"/>
@@ -9955,10 +9973,10 @@
       <c r="B166" s="62"/>
       <c r="C166" s="45"/>
       <c r="D166" s="60" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="E166" s="20" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="F166" s="21">
         <v>4</v>
@@ -9971,7 +9989,7 @@
         <v>170</v>
       </c>
       <c r="I166" s="37" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="J166" s="12">
         <f t="shared" si="12"/>
@@ -9997,10 +10015,10 @@
       <c r="B167" s="62"/>
       <c r="C167" s="45"/>
       <c r="D167" s="60" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="E167" s="20" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F167" s="21">
         <v>4</v>
@@ -10013,7 +10031,7 @@
         <v>174</v>
       </c>
       <c r="I167" s="37" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="J167" s="12">
         <f t="shared" si="12"/>
@@ -10039,10 +10057,10 @@
       <c r="B168" s="62"/>
       <c r="C168" s="45"/>
       <c r="D168" s="60" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="E168" s="20" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="F168" s="21">
         <v>1</v>
@@ -10055,7 +10073,7 @@
         <v>178</v>
       </c>
       <c r="I168" s="37" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="J168" s="12">
         <f t="shared" ref="J168:J173" si="14">F167+J167</f>
@@ -10074,7 +10092,7 @@
         <v>13</v>
       </c>
       <c r="O168" s="47" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="P168" s="70"/>
     </row>
@@ -10083,10 +10101,10 @@
       <c r="B169" s="62"/>
       <c r="C169" s="45"/>
       <c r="D169" s="60" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="E169" s="20" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="F169" s="21">
         <v>1</v>
@@ -10099,7 +10117,7 @@
         <v>179</v>
       </c>
       <c r="I169" s="37" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="J169" s="12">
         <f t="shared" si="14"/>
@@ -10125,10 +10143,10 @@
       <c r="B170" s="62"/>
       <c r="C170" s="45"/>
       <c r="D170" s="60" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="E170" s="20" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="F170" s="21">
         <v>1</v>
@@ -10141,7 +10159,7 @@
         <v>17A</v>
       </c>
       <c r="I170" s="37" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="J170" s="12">
         <f t="shared" si="14"/>
@@ -10167,10 +10185,10 @@
       <c r="B171" s="62"/>
       <c r="C171" s="45"/>
       <c r="D171" s="60" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="E171" s="20" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="F171" s="21">
         <v>1</v>
@@ -10183,7 +10201,7 @@
         <v>17B</v>
       </c>
       <c r="I171" s="37" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="J171" s="12">
         <f t="shared" si="14"/>
@@ -10209,10 +10227,10 @@
       <c r="B172" s="62"/>
       <c r="C172" s="45"/>
       <c r="D172" s="60" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="E172" s="20" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F172" s="21">
         <v>2</v>
@@ -10225,7 +10243,7 @@
         <v>17C</v>
       </c>
       <c r="I172" s="37" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="J172" s="12">
         <f t="shared" si="14"/>
@@ -10251,10 +10269,10 @@
       <c r="B173" s="62"/>
       <c r="C173" s="45"/>
       <c r="D173" s="57" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E173" s="64" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F173" s="26">
         <v>130</v>
@@ -10291,7 +10309,7 @@
       <c r="B174" s="62"/>
       <c r="C174" s="54"/>
       <c r="D174" s="65" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="E174" s="65"/>
       <c r="F174" s="66"/>

--- a/Backend/srvdata/T-MAXeeprom.xlsx
+++ b/Backend/srvdata/T-MAXeeprom.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$179</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="572">
   <si>
     <t>EEPROM定义_V1.0_20231027</t>
   </si>
@@ -1088,6 +1088,9 @@
     <t>ip</t>
   </si>
   <si>
+    <t xml:space="preserve"> 10.5.55.5</t>
+  </si>
+  <si>
     <t>以太网协议类型</t>
   </si>
   <si>
@@ -1500,6 +1503,42 @@
   </si>
   <si>
     <t>/*菜单闪烁开关*/</t>
+  </si>
+  <si>
+    <t>秤端IP地址</t>
+  </si>
+  <si>
+    <t>M_SCALE_IP</t>
+  </si>
+  <si>
+    <t>/*秤端IP地址*/</t>
+  </si>
+  <si>
+    <t>10.5.55.5</t>
+  </si>
+  <si>
+    <t>秤端子网掩码</t>
+  </si>
+  <si>
+    <t>M_SCALE_MASK</t>
+  </si>
+  <si>
+    <t>/*秤端子网掩码*/</t>
+  </si>
+  <si>
+    <t>255.255.255.0</t>
+  </si>
+  <si>
+    <t>秤端网关</t>
+  </si>
+  <si>
+    <t>M_SCALE_GATEWAY</t>
+  </si>
+  <si>
+    <t>/*秤端网关*/</t>
+  </si>
+  <si>
+    <t>10.5.55.1</t>
   </si>
   <si>
     <t>客户菜单地址</t>
@@ -3089,7 +3128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S176"/>
+  <dimension ref="A1:S179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.11666666666667" customWidth="1"/>
@@ -7587,7 +7626,7 @@
         <v>1</v>
       </c>
       <c r="O97" s="12" t="s">
-        <v>273</v>
+        <v>329</v>
       </c>
       <c r="P97" s="12" t="s">
         <v>282</v>
@@ -7600,10 +7639,10 @@
       <c r="B98" s="17"/>
       <c r="C98" s="18"/>
       <c r="D98" s="19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F98" s="21">
         <v>1</v>
@@ -7616,7 +7655,7 @@
         <v>BE</v>
       </c>
       <c r="I98" s="24" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J98" s="12">
         <f t="shared" si="5"/>
@@ -7646,10 +7685,10 @@
       <c r="B99" s="17"/>
       <c r="C99" s="18"/>
       <c r="D99" s="19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E99" s="20" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F99" s="21">
         <v>1</v>
@@ -7662,7 +7701,7 @@
         <v>BF</v>
       </c>
       <c r="I99" s="24" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J99" s="12">
         <f t="shared" si="5"/>
@@ -7694,10 +7733,10 @@
       <c r="B100" s="17"/>
       <c r="C100" s="18"/>
       <c r="D100" s="19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E100" s="20" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F100" s="21">
         <v>1</v>
@@ -7710,7 +7749,7 @@
         <v>C0</v>
       </c>
       <c r="I100" s="24" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="J100" s="12">
         <f t="shared" si="5"/>
@@ -7740,10 +7779,10 @@
       <c r="B101" s="17"/>
       <c r="C101" s="18"/>
       <c r="D101" s="19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E101" s="20" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F101" s="21">
         <v>1</v>
@@ -7756,7 +7795,7 @@
         <v>C1</v>
       </c>
       <c r="I101" s="24" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J101" s="12">
         <f t="shared" si="5"/>
@@ -7788,10 +7827,10 @@
       <c r="B102" s="17"/>
       <c r="C102" s="18"/>
       <c r="D102" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E102" s="20" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F102" s="21">
         <v>1</v>
@@ -7804,7 +7843,7 @@
         <v>C2</v>
       </c>
       <c r="I102" s="24" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J102" s="12">
         <f t="shared" si="5"/>
@@ -7834,10 +7873,10 @@
       <c r="B103" s="17"/>
       <c r="C103" s="18"/>
       <c r="D103" s="37" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E103" s="38" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F103" s="21">
         <v>1</v>
@@ -7850,7 +7889,7 @@
         <v>C3</v>
       </c>
       <c r="I103" s="47" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J103" s="12">
         <f t="shared" si="5"/>
@@ -7880,10 +7919,10 @@
       <c r="B104" s="17"/>
       <c r="C104" s="18"/>
       <c r="D104" s="37" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E104" s="38" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F104" s="21">
         <v>1</v>
@@ -7896,7 +7935,7 @@
         <v>C4</v>
       </c>
       <c r="I104" s="47" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J104" s="12">
         <f t="shared" si="5"/>
@@ -7926,10 +7965,10 @@
       <c r="B105" s="17"/>
       <c r="C105" s="18"/>
       <c r="D105" s="37" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E105" s="38" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F105" s="21">
         <v>1</v>
@@ -7942,7 +7981,7 @@
         <v>C5</v>
       </c>
       <c r="I105" s="47" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J105" s="12">
         <f t="shared" si="5"/>
@@ -7972,10 +8011,10 @@
       <c r="B106" s="17"/>
       <c r="C106" s="18"/>
       <c r="D106" s="37" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E106" s="38" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F106" s="21">
         <v>1</v>
@@ -7988,7 +8027,7 @@
         <v>C6</v>
       </c>
       <c r="I106" s="47" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J106" s="12">
         <f t="shared" si="5"/>
@@ -8018,10 +8057,10 @@
       <c r="B107" s="17"/>
       <c r="C107" s="18"/>
       <c r="D107" s="37" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E107" s="38" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F107" s="21">
         <v>1</v>
@@ -8034,7 +8073,7 @@
         <v>C7</v>
       </c>
       <c r="I107" s="47" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J107" s="12">
         <f t="shared" si="5"/>
@@ -8064,10 +8103,10 @@
       <c r="B108" s="17"/>
       <c r="C108" s="18"/>
       <c r="D108" s="37" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E108" s="38" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F108" s="21">
         <v>4</v>
@@ -8080,7 +8119,7 @@
         <v>C8</v>
       </c>
       <c r="I108" s="47" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J108" s="12">
         <f t="shared" si="5"/>
@@ -8110,10 +8149,10 @@
       <c r="B109" s="17"/>
       <c r="C109" s="18"/>
       <c r="D109" s="37" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E109" s="38" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F109" s="21">
         <v>1</v>
@@ -8126,7 +8165,7 @@
         <v>CC</v>
       </c>
       <c r="I109" s="47" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J109" s="12">
         <f t="shared" si="5"/>
@@ -8156,10 +8195,10 @@
       <c r="B110" s="17"/>
       <c r="C110" s="18"/>
       <c r="D110" s="37" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E110" s="38" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F110" s="21">
         <v>1</v>
@@ -8172,7 +8211,7 @@
         <v>CD</v>
       </c>
       <c r="I110" s="47" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J110" s="12">
         <f t="shared" si="5"/>
@@ -8189,7 +8228,7 @@
         <v>1</v>
       </c>
       <c r="O110" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P110" s="12" t="s">
         <v>282</v>
@@ -8202,10 +8241,10 @@
       <c r="B111" s="17"/>
       <c r="C111" s="18"/>
       <c r="D111" s="37" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E111" s="38" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F111" s="21">
         <v>2</v>
@@ -8218,7 +8257,7 @@
         <v>CE</v>
       </c>
       <c r="I111" s="47" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J111" s="12">
         <f t="shared" si="5"/>
@@ -8235,7 +8274,7 @@
         <v>1</v>
       </c>
       <c r="O111" s="12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P111" s="12" t="s">
         <v>282</v>
@@ -8248,10 +8287,10 @@
       <c r="B112" s="17"/>
       <c r="C112" s="18"/>
       <c r="D112" s="37" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E112" s="38" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F112" s="21">
         <v>1</v>
@@ -8264,7 +8303,7 @@
         <v>D0</v>
       </c>
       <c r="I112" s="47" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J112" s="12">
         <f t="shared" si="5"/>
@@ -8281,13 +8320,13 @@
         <v>95</v>
       </c>
       <c r="O112" s="12" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P112" s="12" t="s">
         <v>282</v>
       </c>
       <c r="Q112" s="33" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="R112" s="32"/>
     </row>
@@ -8338,17 +8377,17 @@
     <row r="114" ht="20.25" spans="1:18">
       <c r="A114" s="16"/>
       <c r="B114" s="17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C114" s="18">
         <f>SUM(F126,J126)-J114</f>
         <v>25</v>
       </c>
       <c r="D114" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F114" s="21">
         <v>1</v>
@@ -8361,7 +8400,7 @@
         <v>DA</v>
       </c>
       <c r="I114" s="24" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J114" s="12">
         <f t="shared" si="5"/>
@@ -8381,7 +8420,7 @@
         <v>273</v>
       </c>
       <c r="P114" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q114" s="33"/>
       <c r="R114" s="32"/>
@@ -8391,10 +8430,10 @@
       <c r="B115" s="17"/>
       <c r="C115" s="18"/>
       <c r="D115" s="19" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E115" s="20" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F115" s="21">
         <v>1</v>
@@ -8407,7 +8446,7 @@
         <v>DB</v>
       </c>
       <c r="I115" s="24" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J115" s="12">
         <f t="shared" si="5"/>
@@ -8424,10 +8463,10 @@
         <v>1</v>
       </c>
       <c r="O115" s="12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="P115" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q115" s="33"/>
       <c r="R115" s="32"/>
@@ -8437,10 +8476,10 @@
       <c r="B116" s="17"/>
       <c r="C116" s="18"/>
       <c r="D116" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E116" s="20" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F116" s="21">
         <v>2</v>
@@ -8453,7 +8492,7 @@
         <v>DC</v>
       </c>
       <c r="I116" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J116" s="12">
         <f t="shared" si="5"/>
@@ -8470,10 +8509,10 @@
         <v>1</v>
       </c>
       <c r="O116" s="12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P116" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q116" s="33"/>
       <c r="R116" s="32"/>
@@ -8483,10 +8522,10 @@
       <c r="B117" s="17"/>
       <c r="C117" s="18"/>
       <c r="D117" s="19" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E117" s="20" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F117" s="21">
         <v>2</v>
@@ -8499,7 +8538,7 @@
         <v>DE</v>
       </c>
       <c r="I117" s="19" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J117" s="12">
         <f t="shared" si="5"/>
@@ -8516,10 +8555,10 @@
         <v>1</v>
       </c>
       <c r="O117" s="12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P117" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q117" s="33"/>
       <c r="R117" s="32"/>
@@ -8529,10 +8568,10 @@
       <c r="B118" s="17"/>
       <c r="C118" s="18"/>
       <c r="D118" s="19" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E118" s="20" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F118" s="21">
         <v>2</v>
@@ -8545,7 +8584,7 @@
         <v>E0</v>
       </c>
       <c r="I118" s="19" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J118" s="12">
         <f t="shared" si="5"/>
@@ -8562,10 +8601,10 @@
         <v>1</v>
       </c>
       <c r="O118" s="12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P118" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q118" s="33"/>
       <c r="R118" s="32"/>
@@ -8575,10 +8614,10 @@
       <c r="B119" s="17"/>
       <c r="C119" s="18"/>
       <c r="D119" s="19" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E119" s="20" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F119" s="21">
         <v>1</v>
@@ -8591,7 +8630,7 @@
         <v>E2</v>
       </c>
       <c r="I119" s="19" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J119" s="12">
         <f t="shared" si="5"/>
@@ -8611,7 +8650,7 @@
         <v>96</v>
       </c>
       <c r="P119" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q119" s="33"/>
       <c r="R119" s="32"/>
@@ -8621,10 +8660,10 @@
       <c r="B120" s="17"/>
       <c r="C120" s="18"/>
       <c r="D120" s="19" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E120" s="20" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F120" s="21">
         <v>1</v>
@@ -8637,7 +8676,7 @@
         <v>E3</v>
       </c>
       <c r="I120" s="19" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J120" s="12">
         <f t="shared" si="5"/>
@@ -8654,10 +8693,10 @@
         <v>1</v>
       </c>
       <c r="O120" s="12" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P120" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q120" s="33"/>
       <c r="R120" s="32"/>
@@ -8667,10 +8706,10 @@
       <c r="B121" s="17"/>
       <c r="C121" s="18"/>
       <c r="D121" s="19" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E121" s="20" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F121" s="21">
         <v>1</v>
@@ -8683,7 +8722,7 @@
         <v>E4</v>
       </c>
       <c r="I121" s="19" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J121" s="12">
         <f t="shared" si="5"/>
@@ -8700,10 +8739,10 @@
         <v>1</v>
       </c>
       <c r="O121" s="12" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P121" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q121" s="33"/>
       <c r="R121" s="32"/>
@@ -8713,10 +8752,10 @@
       <c r="B122" s="17"/>
       <c r="C122" s="18"/>
       <c r="D122" s="19" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E122" s="20" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F122" s="21">
         <v>1</v>
@@ -8729,7 +8768,7 @@
         <v>E5</v>
       </c>
       <c r="I122" s="19" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J122" s="12">
         <f t="shared" si="5"/>
@@ -8749,7 +8788,7 @@
         <v>96</v>
       </c>
       <c r="P122" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q122" s="33"/>
       <c r="R122" s="32"/>
@@ -8759,10 +8798,10 @@
       <c r="B123" s="41"/>
       <c r="C123" s="42"/>
       <c r="D123" s="19" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E123" s="20" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F123" s="21">
         <v>1</v>
@@ -8775,7 +8814,7 @@
         <v>E6</v>
       </c>
       <c r="I123" s="19" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J123" s="12">
         <f t="shared" si="5"/>
@@ -8795,7 +8834,7 @@
         <v>235</v>
       </c>
       <c r="P123" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q123" s="52"/>
     </row>
@@ -8804,10 +8843,10 @@
       <c r="B124" s="41"/>
       <c r="C124" s="42"/>
       <c r="D124" s="19" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E124" s="20" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F124" s="21">
         <v>1</v>
@@ -8820,10 +8859,10 @@
         <v>E7</v>
       </c>
       <c r="I124" s="19" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J124" s="12">
-        <f t="shared" ref="J124:J143" si="7">F123+J123</f>
+        <f t="shared" ref="J124:J146" si="7">F123+J123</f>
         <v>231</v>
       </c>
       <c r="K124" s="12" t="s">
@@ -8840,7 +8879,7 @@
         <v>96</v>
       </c>
       <c r="P124" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q124" s="52"/>
     </row>
@@ -8849,10 +8888,10 @@
       <c r="B125" s="41"/>
       <c r="C125" s="42"/>
       <c r="D125" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E125" s="20" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F125" s="21">
         <v>1</v>
@@ -8865,7 +8904,7 @@
         <v>E8</v>
       </c>
       <c r="I125" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J125" s="12">
         <f t="shared" si="7"/>
@@ -8885,7 +8924,7 @@
         <v>14</v>
       </c>
       <c r="P125" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q125" s="52"/>
     </row>
@@ -8906,7 +8945,7 @@
         <v>21</v>
       </c>
       <c r="H126" s="27" t="str">
-        <f t="shared" ref="H126:H145" si="8">DEC2HEX(J126)</f>
+        <f t="shared" ref="H126:H148" si="8">DEC2HEX(J126)</f>
         <v>E9</v>
       </c>
       <c r="I126" s="30"/>
@@ -8928,7 +8967,7 @@
         <v>14</v>
       </c>
       <c r="P126" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q126" s="33"/>
       <c r="R126" s="32"/>
@@ -8936,17 +8975,17 @@
     <row r="127" ht="20.25" spans="1:18">
       <c r="A127" s="16"/>
       <c r="B127" s="43" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C127" s="44">
         <f>SUM(F132,J132)-J127</f>
         <v>20</v>
       </c>
       <c r="D127" s="19" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E127" s="20" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F127" s="21">
         <v>8</v>
@@ -8959,7 +8998,7 @@
         <v>F3</v>
       </c>
       <c r="I127" s="19" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J127" s="12">
         <f t="shared" si="7"/>
@@ -8979,7 +9018,7 @@
         <v>14</v>
       </c>
       <c r="P127" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q127" s="33"/>
       <c r="R127" s="32"/>
@@ -8989,10 +9028,10 @@
       <c r="B128" s="16"/>
       <c r="C128" s="45"/>
       <c r="D128" s="19" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E128" s="20" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F128" s="21">
         <v>8</v>
@@ -9005,7 +9044,7 @@
         <v>FB</v>
       </c>
       <c r="I128" s="19" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J128" s="12">
         <f t="shared" si="7"/>
@@ -9025,7 +9064,7 @@
         <v>14</v>
       </c>
       <c r="P128" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q128" s="33"/>
       <c r="R128" s="32"/>
@@ -9035,10 +9074,10 @@
       <c r="B129" s="16"/>
       <c r="C129" s="45"/>
       <c r="D129" s="19" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E129" s="20" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F129" s="21">
         <v>1</v>
@@ -9051,7 +9090,7 @@
         <v>103</v>
       </c>
       <c r="I129" s="24" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J129" s="12">
         <f t="shared" si="7"/>
@@ -9071,7 +9110,7 @@
         <v>14</v>
       </c>
       <c r="P129" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q129" s="34"/>
       <c r="R129" s="32"/>
@@ -9081,10 +9120,10 @@
       <c r="B130" s="16"/>
       <c r="C130" s="45"/>
       <c r="D130" s="19" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E130" s="20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F130" s="21">
         <v>1</v>
@@ -9097,7 +9136,7 @@
         <v>104</v>
       </c>
       <c r="I130" s="24" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J130" s="12">
         <f t="shared" si="7"/>
@@ -9117,10 +9156,10 @@
         <v>14</v>
       </c>
       <c r="P130" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q130" s="34" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="R130" s="32"/>
     </row>
@@ -9129,10 +9168,10 @@
       <c r="B131" s="16"/>
       <c r="C131" s="45"/>
       <c r="D131" s="19" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E131" s="20" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F131" s="21">
         <v>1</v>
@@ -9145,7 +9184,7 @@
         <v>105</v>
       </c>
       <c r="I131" s="24" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J131" s="12">
         <f t="shared" si="7"/>
@@ -9167,10 +9206,10 @@
         <v>14</v>
       </c>
       <c r="P131" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q131" s="34" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="R131" s="32"/>
     </row>
@@ -9179,7 +9218,7 @@
       <c r="B132" s="53"/>
       <c r="C132" s="54"/>
       <c r="D132" s="55" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E132" s="20"/>
       <c r="F132" s="21">
@@ -9211,27 +9250,27 @@
         <v>14</v>
       </c>
       <c r="P132" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q132" s="34"/>
       <c r="R132" s="32"/>
     </row>
     <row r="133" ht="20.25" spans="1:18">
       <c r="A133" s="17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B133" s="43" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C133" s="44">
-        <f>SUM(F143,J143)-J133</f>
-        <v>66</v>
+        <f>SUM(F146,J146)-J133</f>
+        <v>78</v>
       </c>
       <c r="D133" s="19" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E133" s="20" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F133" s="21">
         <v>4</v>
@@ -9244,7 +9283,7 @@
         <v>107</v>
       </c>
       <c r="I133" s="24" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J133" s="12">
         <f t="shared" si="7"/>
@@ -9261,10 +9300,10 @@
         <v>1</v>
       </c>
       <c r="O133" s="12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P133" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q133" s="34"/>
       <c r="R133" s="32"/>
@@ -9274,10 +9313,10 @@
       <c r="B134" s="16"/>
       <c r="C134" s="45"/>
       <c r="D134" s="19" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E134" s="20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F134" s="21">
         <v>4</v>
@@ -9290,7 +9329,7 @@
         <v>10B</v>
       </c>
       <c r="I134" s="24" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J134" s="12">
         <f t="shared" si="7"/>
@@ -9307,10 +9346,10 @@
         <v>1</v>
       </c>
       <c r="O134" s="12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P134" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q134" s="34"/>
       <c r="R134" s="32"/>
@@ -9320,10 +9359,10 @@
       <c r="B135" s="16"/>
       <c r="C135" s="45"/>
       <c r="D135" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E135" s="20" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F135" s="21">
         <v>1</v>
@@ -9336,7 +9375,7 @@
         <v>10F</v>
       </c>
       <c r="I135" s="24" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J135" s="12">
         <f t="shared" si="7"/>
@@ -9356,7 +9395,7 @@
         <v>14</v>
       </c>
       <c r="P135" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q135" s="34"/>
       <c r="R135" s="32"/>
@@ -9366,10 +9405,10 @@
       <c r="B136" s="16"/>
       <c r="C136" s="45"/>
       <c r="D136" s="19" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E136" s="20" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F136" s="21">
         <v>1</v>
@@ -9382,7 +9421,7 @@
         <v>110</v>
       </c>
       <c r="I136" s="24" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J136" s="12">
         <f t="shared" si="7"/>
@@ -9404,10 +9443,10 @@
         <v>14</v>
       </c>
       <c r="P136" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q136" s="34" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="R136" s="32"/>
     </row>
@@ -9416,10 +9455,10 @@
       <c r="B137" s="16"/>
       <c r="C137" s="45"/>
       <c r="D137" s="56" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E137" s="20" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F137" s="21">
         <v>4</v>
@@ -9432,7 +9471,7 @@
         <v>111</v>
       </c>
       <c r="I137" s="24" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J137" s="12">
         <f t="shared" si="7"/>
@@ -9449,10 +9488,10 @@
         <v>1</v>
       </c>
       <c r="O137" s="12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P137" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q137" s="34"/>
       <c r="R137" s="32"/>
@@ -9462,10 +9501,10 @@
       <c r="B138" s="16"/>
       <c r="C138" s="45"/>
       <c r="D138" s="56" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E138" s="20" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F138" s="21">
         <v>4</v>
@@ -9478,7 +9517,7 @@
         <v>115</v>
       </c>
       <c r="I138" s="24" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J138" s="12">
         <f t="shared" si="7"/>
@@ -9495,10 +9534,10 @@
         <v>1</v>
       </c>
       <c r="O138" s="12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P138" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q138" s="34"/>
       <c r="R138" s="32"/>
@@ -9508,10 +9547,10 @@
       <c r="B139" s="16"/>
       <c r="C139" s="45"/>
       <c r="D139" s="19" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E139" s="20" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F139" s="21">
         <v>1</v>
@@ -9524,7 +9563,7 @@
         <v>119</v>
       </c>
       <c r="I139" s="24" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J139" s="12">
         <f t="shared" si="7"/>
@@ -9546,10 +9585,10 @@
         <v>14</v>
       </c>
       <c r="P139" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q139" s="69" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="R139" s="32"/>
     </row>
@@ -9558,10 +9597,10 @@
       <c r="B140" s="16"/>
       <c r="C140" s="45"/>
       <c r="D140" s="56" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E140" s="20" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F140" s="21">
         <v>8</v>
@@ -9574,7 +9613,7 @@
         <v>11A</v>
       </c>
       <c r="I140" s="24" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J140" s="12">
         <f t="shared" si="7"/>
@@ -9594,7 +9633,7 @@
         <v>75</v>
       </c>
       <c r="P140" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q140" s="34"/>
       <c r="R140" s="32"/>
@@ -9604,10 +9643,10 @@
       <c r="B141" s="16"/>
       <c r="C141" s="45"/>
       <c r="D141" s="56" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E141" s="20" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F141" s="21">
         <v>8</v>
@@ -9620,7 +9659,7 @@
         <v>122</v>
       </c>
       <c r="I141" s="24" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J141" s="12">
         <f t="shared" si="7"/>
@@ -9640,7 +9679,7 @@
         <v>75</v>
       </c>
       <c r="P141" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q141" s="34"/>
       <c r="R141" s="32"/>
@@ -9650,10 +9689,10 @@
       <c r="B142" s="16"/>
       <c r="C142" s="45"/>
       <c r="D142" s="56" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E142" s="20" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F142" s="21">
         <v>1</v>
@@ -9666,7 +9705,7 @@
         <v>12A</v>
       </c>
       <c r="I142" s="24" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J142" s="12">
         <f t="shared" si="7"/>
@@ -9688,189 +9727,186 @@
         <v>235</v>
       </c>
       <c r="P142" s="12" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q142" s="34" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="R142" s="32"/>
     </row>
     <row r="143" ht="20.25" spans="1:18">
       <c r="A143" s="17"/>
-      <c r="B143" s="53"/>
-      <c r="C143" s="54"/>
-      <c r="D143" s="57" t="s">
-        <v>179</v>
-      </c>
-      <c r="E143" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="F143" s="26">
-        <v>30</v>
+      <c r="B143" s="16"/>
+      <c r="C143" s="45"/>
+      <c r="D143" s="56" t="s">
+        <v>468</v>
+      </c>
+      <c r="E143" s="20" t="s">
+        <v>469</v>
+      </c>
+      <c r="F143" s="21">
+        <v>4</v>
       </c>
       <c r="G143" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="H143" s="27" t="str">
+      <c r="H143" s="23" t="str">
         <f t="shared" si="8"/>
         <v>12B</v>
       </c>
-      <c r="I143" s="30"/>
-      <c r="J143" s="31">
+      <c r="I143" s="24" t="s">
+        <v>470</v>
+      </c>
+      <c r="J143" s="12">
         <f t="shared" si="7"/>
         <v>299</v>
       </c>
       <c r="K143" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="L143" s="12"/>
+      <c r="L143" s="12" t="s">
+        <v>328</v>
+      </c>
       <c r="M143" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N143" s="12">
         <v>1</v>
       </c>
       <c r="O143" s="12" t="s">
-        <v>14</v>
+        <v>471</v>
       </c>
       <c r="P143" s="12" t="s">
-        <v>418</v>
+        <v>282</v>
       </c>
       <c r="Q143" s="34"/>
       <c r="R143" s="32"/>
     </row>
-    <row r="144" s="3" customFormat="1" ht="20.25" spans="1:18">
+    <row r="144" ht="20.25" spans="1:18">
       <c r="A144" s="17"/>
-      <c r="B144" s="58" t="s">
-        <v>467</v>
-      </c>
-      <c r="C144" s="59"/>
-      <c r="D144" s="60" t="s">
-        <v>468</v>
-      </c>
-      <c r="E144" s="38" t="s">
-        <v>469</v>
+      <c r="B144" s="16"/>
+      <c r="C144" s="45"/>
+      <c r="D144" s="56" t="s">
+        <v>472</v>
+      </c>
+      <c r="E144" s="20" t="s">
+        <v>473</v>
       </c>
       <c r="F144" s="21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G144" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="H144" s="40" t="str">
+      <c r="H144" s="23" t="str">
         <f t="shared" si="8"/>
-        <v>149</v>
-      </c>
-      <c r="I144" s="47" t="s">
-        <v>470</v>
+        <v>12F</v>
+      </c>
+      <c r="I144" s="24" t="s">
+        <v>474</v>
       </c>
       <c r="J144" s="12">
-        <f t="shared" ref="J143:J151" si="9">F143+J143</f>
-        <v>329</v>
+        <f t="shared" si="7"/>
+        <v>303</v>
       </c>
       <c r="K144" s="12" t="s">
         <v>23</v>
       </c>
       <c r="L144" s="12" t="s">
-        <v>231</v>
+        <v>328</v>
       </c>
       <c r="M144" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N144" s="12">
         <v>1</v>
       </c>
       <c r="O144" s="12" t="s">
-        <v>14</v>
+        <v>475</v>
       </c>
       <c r="P144" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q144" s="70" t="s">
-        <v>457</v>
-      </c>
-      <c r="R144" s="3" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="145" s="3" customFormat="1" ht="20.25" spans="1:17">
+        <v>282</v>
+      </c>
+      <c r="Q144" s="34"/>
+      <c r="R144" s="32"/>
+    </row>
+    <row r="145" ht="20.25" spans="1:18">
       <c r="A145" s="17"/>
-      <c r="B145" s="58"/>
-      <c r="C145" s="61"/>
-      <c r="D145" s="60" t="s">
-        <v>473</v>
-      </c>
-      <c r="E145" s="38" t="s">
-        <v>474</v>
+      <c r="B145" s="16"/>
+      <c r="C145" s="45"/>
+      <c r="D145" s="56" t="s">
+        <v>476</v>
+      </c>
+      <c r="E145" s="20" t="s">
+        <v>477</v>
       </c>
       <c r="F145" s="21">
+        <v>4</v>
+      </c>
+      <c r="G145" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H145" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>133</v>
+      </c>
+      <c r="I145" s="24" t="s">
+        <v>478</v>
+      </c>
+      <c r="J145" s="12">
+        <f t="shared" si="7"/>
+        <v>307</v>
+      </c>
+      <c r="K145" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L145" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="M145" s="12">
         <v>2</v>
       </c>
-      <c r="G145" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H145" s="40" t="str">
+      <c r="N145" s="12">
+        <v>1</v>
+      </c>
+      <c r="O145" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="P145" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q145" s="34"/>
+      <c r="R145" s="32"/>
+    </row>
+    <row r="146" ht="20.25" spans="1:18">
+      <c r="A146" s="17"/>
+      <c r="B146" s="53"/>
+      <c r="C146" s="54"/>
+      <c r="D146" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="E146" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="F146" s="26">
+        <v>30</v>
+      </c>
+      <c r="G146" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H146" s="23" t="str">
         <f t="shared" si="8"/>
-        <v>14A</v>
-      </c>
-      <c r="I145" s="47" t="s">
-        <v>475</v>
-      </c>
-      <c r="J145" s="12">
-        <f t="shared" si="9"/>
-        <v>330</v>
-      </c>
-      <c r="K145" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L145" s="12"/>
-      <c r="M145" s="12">
-        <v>0</v>
-      </c>
-      <c r="N145" s="12">
-        <v>1</v>
-      </c>
-      <c r="O145" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="P145" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q145" s="70"/>
-    </row>
-    <row r="146" customFormat="1" ht="20.25" spans="1:18">
-      <c r="A146" s="17"/>
-      <c r="B146" s="62"/>
-      <c r="C146" s="45"/>
-      <c r="D146" s="60" t="s">
-        <v>476</v>
-      </c>
-      <c r="E146" s="38" t="s">
-        <v>477</v>
-      </c>
-      <c r="F146" s="21">
-        <v>1</v>
-      </c>
-      <c r="G146" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H146" s="40" t="str">
-        <f t="shared" ref="H146:H151" si="10">DEC2HEX(J146)</f>
-        <v>14C</v>
-      </c>
-      <c r="I146" s="37" t="s">
-        <v>478</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="I146" s="30"/>
       <c r="J146" s="12">
-        <f t="shared" si="9"/>
-        <v>332</v>
+        <f t="shared" si="7"/>
+        <v>311</v>
       </c>
       <c r="K146" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="L146" s="12" t="s">
-        <v>231</v>
-      </c>
+      <c r="L146" s="12"/>
       <c r="M146" s="12">
         <v>0</v>
       </c>
@@ -9881,25 +9917,23 @@
         <v>14</v>
       </c>
       <c r="P146" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q146" s="33" t="s">
-        <v>457</v>
-      </c>
-      <c r="R146" s="71" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="147" customFormat="1" ht="20.25" spans="1:18">
+        <v>419</v>
+      </c>
+      <c r="Q146" s="34"/>
+      <c r="R146" s="32"/>
+    </row>
+    <row r="147" s="3" customFormat="1" ht="20.25" spans="1:18">
       <c r="A147" s="17"/>
-      <c r="B147" s="62"/>
-      <c r="C147" s="45"/>
+      <c r="B147" s="58" t="s">
+        <v>480</v>
+      </c>
+      <c r="C147" s="59"/>
       <c r="D147" s="60" t="s">
-        <v>480</v>
-      </c>
-      <c r="E147" s="20" t="s">
         <v>481</v>
       </c>
+      <c r="E147" s="38" t="s">
+        <v>482</v>
+      </c>
       <c r="F147" s="21">
         <v>1</v>
       </c>
@@ -9907,20 +9941,22 @@
         <v>21</v>
       </c>
       <c r="H147" s="40" t="str">
-        <f t="shared" si="10"/>
-        <v>14D</v>
-      </c>
-      <c r="I147" s="37" t="s">
-        <v>482</v>
+        <f t="shared" si="8"/>
+        <v>155</v>
+      </c>
+      <c r="I147" s="47" t="s">
+        <v>483</v>
       </c>
       <c r="J147" s="12">
-        <f t="shared" si="9"/>
-        <v>333</v>
+        <f t="shared" ref="J146:J154" si="9">F146+J146</f>
+        <v>341</v>
       </c>
       <c r="K147" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="L147" s="12"/>
+      <c r="L147" s="12" t="s">
+        <v>231</v>
+      </c>
       <c r="M147" s="12">
         <v>0</v>
       </c>
@@ -9931,40 +9967,44 @@
         <v>14</v>
       </c>
       <c r="P147" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q147" s="33"/>
-      <c r="R147" s="71"/>
-    </row>
-    <row r="148" customFormat="1" ht="20.25" spans="1:18">
+        <v>484</v>
+      </c>
+      <c r="Q147" s="70" t="s">
+        <v>458</v>
+      </c>
+      <c r="R147" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="148" s="3" customFormat="1" ht="20.25" spans="1:17">
       <c r="A148" s="17"/>
-      <c r="B148" s="62"/>
-      <c r="C148" s="45"/>
+      <c r="B148" s="58"/>
+      <c r="C148" s="61"/>
       <c r="D148" s="60" t="s">
-        <v>483</v>
-      </c>
-      <c r="E148" s="20" t="s">
-        <v>484</v>
+        <v>486</v>
+      </c>
+      <c r="E148" s="38" t="s">
+        <v>487</v>
       </c>
       <c r="F148" s="21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G148" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H148" s="40" t="str">
-        <f t="shared" si="10"/>
-        <v>14E</v>
-      </c>
-      <c r="I148" s="37" t="s">
-        <v>485</v>
+        <f t="shared" si="8"/>
+        <v>156</v>
+      </c>
+      <c r="I148" s="47" t="s">
+        <v>488</v>
       </c>
       <c r="J148" s="12">
         <f t="shared" si="9"/>
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="K148" s="12" t="s">
-        <v>189</v>
+        <v>23</v>
       </c>
       <c r="L148" s="12"/>
       <c r="M148" s="12">
@@ -9974,63 +10014,64 @@
         <v>1</v>
       </c>
       <c r="O148" s="12" t="s">
-        <v>486</v>
+        <v>14</v>
       </c>
       <c r="P148" s="12" t="s">
-        <v>418</v>
-      </c>
-      <c r="Q148" s="33" t="s">
-        <v>487</v>
-      </c>
-      <c r="R148" s="71"/>
+        <v>484</v>
+      </c>
+      <c r="Q148" s="70"/>
     </row>
     <row r="149" customFormat="1" ht="20.25" spans="1:18">
       <c r="A149" s="17"/>
       <c r="B149" s="62"/>
       <c r="C149" s="45"/>
       <c r="D149" s="60" t="s">
-        <v>488</v>
-      </c>
-      <c r="E149" s="20" t="s">
         <v>489</v>
       </c>
+      <c r="E149" s="38" t="s">
+        <v>490</v>
+      </c>
       <c r="F149" s="21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G149" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H149" s="40" t="str">
-        <f t="shared" si="10"/>
-        <v>152</v>
+        <f t="shared" ref="H149:H154" si="10">DEC2HEX(J149)</f>
+        <v>158</v>
       </c>
       <c r="I149" s="37" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J149" s="12">
         <f t="shared" si="9"/>
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="K149" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="L149" s="12"/>
+        <v>23</v>
+      </c>
+      <c r="L149" s="12" t="s">
+        <v>231</v>
+      </c>
       <c r="M149" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N149" s="12">
         <v>1</v>
       </c>
       <c r="O149" s="12" t="s">
-        <v>491</v>
+        <v>14</v>
       </c>
       <c r="P149" s="12" t="s">
-        <v>418</v>
+        <v>484</v>
       </c>
       <c r="Q149" s="33" t="s">
+        <v>458</v>
+      </c>
+      <c r="R149" s="71" t="s">
         <v>492</v>
       </c>
-      <c r="R149" s="71"/>
     </row>
     <row r="150" customFormat="1" ht="20.25" spans="1:18">
       <c r="A150" s="17"/>
@@ -10050,21 +10091,19 @@
       </c>
       <c r="H150" s="40" t="str">
         <f t="shared" si="10"/>
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I150" s="37" t="s">
         <v>495</v>
       </c>
       <c r="J150" s="12">
         <f t="shared" si="9"/>
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K150" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="L150" s="12" t="s">
-        <v>231</v>
-      </c>
+      <c r="L150" s="12"/>
       <c r="M150" s="12">
         <v>0</v>
       </c>
@@ -10075,15 +10114,15 @@
         <v>14</v>
       </c>
       <c r="P150" s="12" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="Q150" s="33"/>
       <c r="R150" s="71"/>
     </row>
-    <row r="151" s="2" customFormat="1" ht="20.25" spans="1:18">
+    <row r="151" customFormat="1" ht="20.25" spans="1:18">
       <c r="A151" s="17"/>
-      <c r="B151" s="58"/>
-      <c r="C151" s="63"/>
+      <c r="B151" s="62"/>
+      <c r="C151" s="45"/>
       <c r="D151" s="60" t="s">
         <v>496</v>
       </c>
@@ -10091,28 +10130,26 @@
         <v>497</v>
       </c>
       <c r="F151" s="21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G151" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H151" s="40" t="str">
         <f t="shared" si="10"/>
-        <v>157</v>
+        <v>15A</v>
       </c>
       <c r="I151" s="37" t="s">
         <v>498</v>
       </c>
       <c r="J151" s="12">
         <f t="shared" si="9"/>
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="K151" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="L151" s="12" t="s">
-        <v>231</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="L151" s="12"/>
       <c r="M151" s="12">
         <v>0</v>
       </c>
@@ -10120,58 +10157,62 @@
         <v>1</v>
       </c>
       <c r="O151" s="12" t="s">
-        <v>14</v>
+        <v>499</v>
       </c>
       <c r="P151" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q151" s="52"/>
-      <c r="R151" s="72"/>
+        <v>419</v>
+      </c>
+      <c r="Q151" s="33" t="s">
+        <v>500</v>
+      </c>
+      <c r="R151" s="71"/>
     </row>
     <row r="152" customFormat="1" ht="20.25" spans="1:18">
       <c r="A152" s="17"/>
       <c r="B152" s="62"/>
       <c r="C152" s="45"/>
       <c r="D152" s="60" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E152" s="20" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F152" s="21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G152" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H152" s="40" t="str">
-        <f t="shared" ref="H152:H167" si="11">DEC2HEX(J152)</f>
-        <v>158</v>
+        <f t="shared" si="10"/>
+        <v>15E</v>
       </c>
       <c r="I152" s="37" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="J152" s="12">
-        <f t="shared" ref="J152:J167" si="12">F151+J151</f>
-        <v>344</v>
+        <f t="shared" si="9"/>
+        <v>350</v>
       </c>
       <c r="K152" s="12" t="s">
-        <v>23</v>
+        <v>189</v>
       </c>
       <c r="L152" s="12"/>
       <c r="M152" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N152" s="12">
         <v>1</v>
       </c>
       <c r="O152" s="12" t="s">
-        <v>14</v>
+        <v>504</v>
       </c>
       <c r="P152" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q152" s="33"/>
+        <v>419</v>
+      </c>
+      <c r="Q152" s="33" t="s">
+        <v>505</v>
+      </c>
       <c r="R152" s="71"/>
     </row>
     <row r="153" customFormat="1" ht="20.25" spans="1:18">
@@ -10179,10 +10220,10 @@
       <c r="B153" s="62"/>
       <c r="C153" s="45"/>
       <c r="D153" s="60" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="E153" s="20" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F153" s="21">
         <v>1</v>
@@ -10191,20 +10232,22 @@
         <v>21</v>
       </c>
       <c r="H153" s="40" t="str">
-        <f t="shared" si="11"/>
-        <v>15A</v>
+        <f t="shared" si="10"/>
+        <v>162</v>
       </c>
       <c r="I153" s="37" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="J153" s="12">
-        <f t="shared" si="12"/>
-        <v>346</v>
+        <f t="shared" si="9"/>
+        <v>354</v>
       </c>
       <c r="K153" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="L153" s="12"/>
+      <c r="L153" s="12" t="s">
+        <v>231</v>
+      </c>
       <c r="M153" s="12">
         <v>0</v>
       </c>
@@ -10215,20 +10258,20 @@
         <v>14</v>
       </c>
       <c r="P153" s="12" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="Q153" s="33"/>
       <c r="R153" s="71"/>
     </row>
-    <row r="154" customFormat="1" ht="20.25" spans="1:18">
+    <row r="154" s="2" customFormat="1" ht="20.25" spans="1:18">
       <c r="A154" s="17"/>
-      <c r="B154" s="62"/>
-      <c r="C154" s="45"/>
+      <c r="B154" s="58"/>
+      <c r="C154" s="63"/>
       <c r="D154" s="60" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="E154" s="20" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="F154" s="21">
         <v>1</v>
@@ -10237,20 +10280,22 @@
         <v>21</v>
       </c>
       <c r="H154" s="40" t="str">
-        <f t="shared" si="11"/>
-        <v>15B</v>
+        <f t="shared" si="10"/>
+        <v>163</v>
       </c>
       <c r="I154" s="37" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="J154" s="12">
-        <f t="shared" si="12"/>
-        <v>347</v>
+        <f t="shared" si="9"/>
+        <v>355</v>
       </c>
       <c r="K154" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="L154" s="12"/>
+      <c r="L154" s="12" t="s">
+        <v>231</v>
+      </c>
       <c r="M154" s="12">
         <v>0</v>
       </c>
@@ -10261,20 +10306,20 @@
         <v>14</v>
       </c>
       <c r="P154" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q154" s="33"/>
-      <c r="R154" s="71"/>
+        <v>484</v>
+      </c>
+      <c r="Q154" s="52"/>
+      <c r="R154" s="72"/>
     </row>
     <row r="155" customFormat="1" ht="20.25" spans="1:18">
       <c r="A155" s="17"/>
       <c r="B155" s="62"/>
       <c r="C155" s="45"/>
       <c r="D155" s="60" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E155" s="20" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="F155" s="21">
         <v>2</v>
@@ -10283,15 +10328,15 @@
         <v>21</v>
       </c>
       <c r="H155" s="40" t="str">
-        <f t="shared" si="11"/>
-        <v>15C</v>
+        <f t="shared" ref="H155:H170" si="11">DEC2HEX(J155)</f>
+        <v>164</v>
       </c>
       <c r="I155" s="37" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="J155" s="12">
-        <f t="shared" si="12"/>
-        <v>348</v>
+        <f t="shared" ref="J155:J170" si="12">F154+J154</f>
+        <v>356</v>
       </c>
       <c r="K155" s="12" t="s">
         <v>23</v>
@@ -10307,7 +10352,7 @@
         <v>14</v>
       </c>
       <c r="P155" s="12" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="Q155" s="33"/>
       <c r="R155" s="71"/>
@@ -10317,10 +10362,10 @@
       <c r="B156" s="62"/>
       <c r="C156" s="45"/>
       <c r="D156" s="60" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E156" s="20" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F156" s="21">
         <v>1</v>
@@ -10330,14 +10375,14 @@
       </c>
       <c r="H156" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>15E</v>
+        <v>166</v>
       </c>
       <c r="I156" s="37" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="J156" s="12">
         <f t="shared" si="12"/>
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="K156" s="12" t="s">
         <v>23</v>
@@ -10353,7 +10398,7 @@
         <v>14</v>
       </c>
       <c r="P156" s="12" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="Q156" s="33"/>
       <c r="R156" s="71"/>
@@ -10363,10 +10408,10 @@
       <c r="B157" s="62"/>
       <c r="C157" s="45"/>
       <c r="D157" s="60" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E157" s="20" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="F157" s="21">
         <v>1</v>
@@ -10376,14 +10421,14 @@
       </c>
       <c r="H157" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>15F</v>
+        <v>167</v>
       </c>
       <c r="I157" s="37" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="J157" s="12">
         <f t="shared" si="12"/>
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="K157" s="12" t="s">
         <v>23</v>
@@ -10399,7 +10444,7 @@
         <v>14</v>
       </c>
       <c r="P157" s="12" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="Q157" s="33"/>
       <c r="R157" s="71"/>
@@ -10409,10 +10454,10 @@
       <c r="B158" s="62"/>
       <c r="C158" s="45"/>
       <c r="D158" s="60" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E158" s="20" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F158" s="21">
         <v>2</v>
@@ -10422,14 +10467,14 @@
       </c>
       <c r="H158" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="I158" s="37" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="J158" s="12">
         <f t="shared" si="12"/>
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="K158" s="12" t="s">
         <v>23</v>
@@ -10445,7 +10490,7 @@
         <v>14</v>
       </c>
       <c r="P158" s="12" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="Q158" s="33"/>
       <c r="R158" s="71"/>
@@ -10455,10 +10500,10 @@
       <c r="B159" s="62"/>
       <c r="C159" s="45"/>
       <c r="D159" s="60" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E159" s="20" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F159" s="21">
         <v>1</v>
@@ -10468,14 +10513,14 @@
       </c>
       <c r="H159" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>162</v>
+        <v>16A</v>
       </c>
       <c r="I159" s="37" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="J159" s="12">
         <f t="shared" si="12"/>
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="K159" s="12" t="s">
         <v>23</v>
@@ -10491,7 +10536,7 @@
         <v>14</v>
       </c>
       <c r="P159" s="12" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="Q159" s="33"/>
       <c r="R159" s="71"/>
@@ -10501,10 +10546,10 @@
       <c r="B160" s="62"/>
       <c r="C160" s="45"/>
       <c r="D160" s="60" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="E160" s="20" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="F160" s="21">
         <v>1</v>
@@ -10514,14 +10559,14 @@
       </c>
       <c r="H160" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>163</v>
+        <v>16B</v>
       </c>
       <c r="I160" s="37" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="J160" s="12">
         <f t="shared" si="12"/>
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="K160" s="12" t="s">
         <v>23</v>
@@ -10537,7 +10582,7 @@
         <v>14</v>
       </c>
       <c r="P160" s="12" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="Q160" s="33"/>
       <c r="R160" s="71"/>
@@ -10547,10 +10592,10 @@
       <c r="B161" s="62"/>
       <c r="C161" s="45"/>
       <c r="D161" s="60" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="E161" s="20" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="F161" s="21">
         <v>2</v>
@@ -10560,14 +10605,14 @@
       </c>
       <c r="H161" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>164</v>
+        <v>16C</v>
       </c>
       <c r="I161" s="37" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="J161" s="12">
         <f t="shared" si="12"/>
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K161" s="12" t="s">
         <v>23</v>
@@ -10583,7 +10628,7 @@
         <v>14</v>
       </c>
       <c r="P161" s="12" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="Q161" s="33"/>
       <c r="R161" s="71"/>
@@ -10593,10 +10638,10 @@
       <c r="B162" s="62"/>
       <c r="C162" s="45"/>
       <c r="D162" s="60" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="E162" s="20" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F162" s="21">
         <v>1</v>
@@ -10606,14 +10651,14 @@
       </c>
       <c r="H162" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>166</v>
+        <v>16E</v>
       </c>
       <c r="I162" s="37" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="J162" s="12">
         <f t="shared" si="12"/>
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="K162" s="12" t="s">
         <v>23</v>
@@ -10629,7 +10674,7 @@
         <v>14</v>
       </c>
       <c r="P162" s="12" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="Q162" s="33"/>
       <c r="R162" s="71"/>
@@ -10639,10 +10684,10 @@
       <c r="B163" s="62"/>
       <c r="C163" s="45"/>
       <c r="D163" s="60" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E163" s="20" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="F163" s="21">
         <v>1</v>
@@ -10652,14 +10697,14 @@
       </c>
       <c r="H163" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>167</v>
+        <v>16F</v>
       </c>
       <c r="I163" s="37" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="J163" s="12">
         <f t="shared" si="12"/>
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="K163" s="12" t="s">
         <v>23</v>
@@ -10675,7 +10720,7 @@
         <v>14</v>
       </c>
       <c r="P163" s="12" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="Q163" s="33"/>
       <c r="R163" s="71"/>
@@ -10685,27 +10730,27 @@
       <c r="B164" s="62"/>
       <c r="C164" s="45"/>
       <c r="D164" s="60" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="E164" s="20" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="F164" s="21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G164" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H164" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I164" s="37" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="J164" s="12">
         <f t="shared" si="12"/>
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="K164" s="12" t="s">
         <v>23</v>
@@ -10721,7 +10766,7 @@
         <v>14</v>
       </c>
       <c r="P164" s="12" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="Q164" s="33"/>
       <c r="R164" s="71"/>
@@ -10731,27 +10776,27 @@
       <c r="B165" s="62"/>
       <c r="C165" s="45"/>
       <c r="D165" s="60" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E165" s="20" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F165" s="21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G165" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H165" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>16C</v>
+        <v>172</v>
       </c>
       <c r="I165" s="37" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="J165" s="12">
         <f t="shared" si="12"/>
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="K165" s="12" t="s">
         <v>23</v>
@@ -10767,7 +10812,7 @@
         <v>14</v>
       </c>
       <c r="P165" s="12" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="Q165" s="33"/>
       <c r="R165" s="71"/>
@@ -10777,27 +10822,27 @@
       <c r="B166" s="62"/>
       <c r="C166" s="45"/>
       <c r="D166" s="60" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="E166" s="20" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="F166" s="21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G166" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H166" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I166" s="37" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="J166" s="12">
         <f t="shared" si="12"/>
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K166" s="12" t="s">
         <v>23</v>
@@ -10813,7 +10858,7 @@
         <v>14</v>
       </c>
       <c r="P166" s="12" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="Q166" s="33"/>
       <c r="R166" s="71"/>
@@ -10823,10 +10868,10 @@
       <c r="B167" s="62"/>
       <c r="C167" s="45"/>
       <c r="D167" s="60" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="E167" s="20" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F167" s="21">
         <v>4</v>
@@ -10839,7 +10884,7 @@
         <v>174</v>
       </c>
       <c r="I167" s="37" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="J167" s="12">
         <f t="shared" si="12"/>
@@ -10859,7 +10904,7 @@
         <v>14</v>
       </c>
       <c r="P167" s="12" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="Q167" s="33"/>
       <c r="R167" s="71"/>
@@ -10869,26 +10914,26 @@
       <c r="B168" s="62"/>
       <c r="C168" s="45"/>
       <c r="D168" s="60" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="E168" s="20" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F168" s="21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G168" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H168" s="40" t="str">
-        <f t="shared" ref="H168:H173" si="13">DEC2HEX(J168)</f>
+        <f t="shared" si="11"/>
         <v>178</v>
       </c>
       <c r="I168" s="37" t="s">
-        <v>531</v>
+        <v>553</v>
       </c>
       <c r="J168" s="12">
-        <f t="shared" ref="J168:J173" si="14">F167+J167</f>
+        <f t="shared" si="12"/>
         <v>376</v>
       </c>
       <c r="K168" s="12" t="s">
@@ -10905,11 +10950,9 @@
         <v>14</v>
       </c>
       <c r="P168" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q168" s="48" t="s">
-        <v>549</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="Q168" s="33"/>
       <c r="R168" s="71"/>
     </row>
     <row r="169" customFormat="1" ht="20.25" spans="1:18">
@@ -10917,27 +10960,27 @@
       <c r="B169" s="62"/>
       <c r="C169" s="45"/>
       <c r="D169" s="60" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="E169" s="20" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F169" s="21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G169" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H169" s="40" t="str">
-        <f t="shared" si="13"/>
-        <v>179</v>
+        <f t="shared" si="11"/>
+        <v>17C</v>
       </c>
       <c r="I169" s="37" t="s">
-        <v>534</v>
+        <v>556</v>
       </c>
       <c r="J169" s="12">
-        <f t="shared" si="14"/>
-        <v>377</v>
+        <f t="shared" si="12"/>
+        <v>380</v>
       </c>
       <c r="K169" s="12" t="s">
         <v>23</v>
@@ -10953,9 +10996,9 @@
         <v>14</v>
       </c>
       <c r="P169" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q169" s="50"/>
+        <v>484</v>
+      </c>
+      <c r="Q169" s="33"/>
       <c r="R169" s="71"/>
     </row>
     <row r="170" customFormat="1" ht="20.25" spans="1:18">
@@ -10963,27 +11006,27 @@
       <c r="B170" s="62"/>
       <c r="C170" s="45"/>
       <c r="D170" s="60" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="E170" s="20" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="F170" s="21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G170" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H170" s="40" t="str">
-        <f t="shared" si="13"/>
-        <v>17A</v>
+        <f t="shared" si="11"/>
+        <v>180</v>
       </c>
       <c r="I170" s="37" t="s">
-        <v>537</v>
+        <v>559</v>
       </c>
       <c r="J170" s="12">
-        <f t="shared" si="14"/>
-        <v>378</v>
+        <f t="shared" si="12"/>
+        <v>384</v>
       </c>
       <c r="K170" s="12" t="s">
         <v>23</v>
@@ -10999,9 +11042,9 @@
         <v>14</v>
       </c>
       <c r="P170" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q170" s="50"/>
+        <v>484</v>
+      </c>
+      <c r="Q170" s="33"/>
       <c r="R170" s="71"/>
     </row>
     <row r="171" customFormat="1" ht="20.25" spans="1:18">
@@ -11009,10 +11052,10 @@
       <c r="B171" s="62"/>
       <c r="C171" s="45"/>
       <c r="D171" s="60" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="E171" s="20" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="F171" s="21">
         <v>1</v>
@@ -11021,15 +11064,15 @@
         <v>21</v>
       </c>
       <c r="H171" s="40" t="str">
-        <f t="shared" si="13"/>
-        <v>17B</v>
+        <f t="shared" ref="H171:H176" si="13">DEC2HEX(J171)</f>
+        <v>184</v>
       </c>
       <c r="I171" s="37" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="J171" s="12">
-        <f t="shared" si="14"/>
-        <v>379</v>
+        <f t="shared" ref="J171:J176" si="14">F170+J170</f>
+        <v>388</v>
       </c>
       <c r="K171" s="12" t="s">
         <v>23</v>
@@ -11045,9 +11088,11 @@
         <v>14</v>
       </c>
       <c r="P171" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q171" s="50"/>
+        <v>484</v>
+      </c>
+      <c r="Q171" s="48" t="s">
+        <v>562</v>
+      </c>
       <c r="R171" s="71"/>
     </row>
     <row r="172" customFormat="1" ht="20.25" spans="1:18">
@@ -11055,27 +11100,27 @@
       <c r="B172" s="62"/>
       <c r="C172" s="45"/>
       <c r="D172" s="60" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="E172" s="20" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="F172" s="21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G172" s="22" t="s">
         <v>21</v>
       </c>
       <c r="H172" s="40" t="str">
         <f t="shared" si="13"/>
-        <v>17C</v>
+        <v>185</v>
       </c>
       <c r="I172" s="37" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="J172" s="12">
         <f t="shared" si="14"/>
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="K172" s="12" t="s">
         <v>23</v>
@@ -11091,35 +11136,37 @@
         <v>14</v>
       </c>
       <c r="P172" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q172" s="51"/>
+        <v>484</v>
+      </c>
+      <c r="Q172" s="50"/>
       <c r="R172" s="71"/>
     </row>
     <row r="173" customFormat="1" ht="20.25" spans="1:18">
       <c r="A173" s="17"/>
       <c r="B173" s="62"/>
       <c r="C173" s="45"/>
-      <c r="D173" s="57" t="s">
-        <v>179</v>
-      </c>
-      <c r="E173" s="64" t="s">
-        <v>179</v>
-      </c>
-      <c r="F173" s="26">
-        <v>130</v>
+      <c r="D173" s="60" t="s">
+        <v>565</v>
+      </c>
+      <c r="E173" s="20" t="s">
+        <v>566</v>
+      </c>
+      <c r="F173" s="21">
+        <v>1</v>
       </c>
       <c r="G173" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="H173" s="27" t="str">
+      <c r="H173" s="40" t="str">
         <f t="shared" si="13"/>
-        <v>17E</v>
-      </c>
-      <c r="I173" s="30"/>
-      <c r="J173" s="31">
+        <v>186</v>
+      </c>
+      <c r="I173" s="37" t="s">
+        <v>550</v>
+      </c>
+      <c r="J173" s="12">
         <f t="shared" si="14"/>
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="K173" s="12" t="s">
         <v>23</v>
@@ -11135,68 +11182,204 @@
         <v>14</v>
       </c>
       <c r="P173" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q173" s="34"/>
+        <v>484</v>
+      </c>
+      <c r="Q173" s="50"/>
       <c r="R173" s="71"/>
     </row>
-    <row r="174" customFormat="1" ht="20.25" spans="1:19">
+    <row r="174" customFormat="1" ht="20.25" spans="1:18">
       <c r="A174" s="17"/>
       <c r="B174" s="62"/>
-      <c r="C174" s="54"/>
-      <c r="D174" s="65" t="s">
-        <v>558</v>
-      </c>
-      <c r="E174" s="65"/>
-      <c r="F174" s="66"/>
-      <c r="G174" s="66"/>
-      <c r="H174" s="66"/>
-      <c r="I174" s="65"/>
-      <c r="J174" s="68"/>
-      <c r="K174" s="12"/>
+      <c r="C174" s="45"/>
+      <c r="D174" s="60" t="s">
+        <v>567</v>
+      </c>
+      <c r="E174" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="F174" s="21">
+        <v>1</v>
+      </c>
+      <c r="G174" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H174" s="40" t="str">
+        <f t="shared" si="13"/>
+        <v>187</v>
+      </c>
+      <c r="I174" s="37" t="s">
+        <v>553</v>
+      </c>
+      <c r="J174" s="12">
+        <f t="shared" si="14"/>
+        <v>391</v>
+      </c>
+      <c r="K174" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="L174" s="12"/>
-      <c r="M174" s="12"/>
-      <c r="N174" s="12"/>
-      <c r="O174" s="12"/>
-      <c r="P174" s="12"/>
-      <c r="Q174" s="12">
-        <f>SUM(F173,J173)</f>
-        <v>512</v>
-      </c>
-      <c r="R174" s="33"/>
-      <c r="S174" s="71"/>
-    </row>
-    <row r="175" ht="16.5" spans="19:19">
-      <c r="S175" s="72"/>
-    </row>
-    <row r="176" ht="16.5" spans="6:6">
-      <c r="F176" s="67"/>
+      <c r="M174" s="12">
+        <v>0</v>
+      </c>
+      <c r="N174" s="12">
+        <v>1</v>
+      </c>
+      <c r="O174" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="P174" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="Q174" s="50"/>
+      <c r="R174" s="71"/>
+    </row>
+    <row r="175" customFormat="1" ht="20.25" spans="1:18">
+      <c r="A175" s="17"/>
+      <c r="B175" s="62"/>
+      <c r="C175" s="45"/>
+      <c r="D175" s="60" t="s">
+        <v>569</v>
+      </c>
+      <c r="E175" s="20" t="s">
+        <v>570</v>
+      </c>
+      <c r="F175" s="21">
+        <v>2</v>
+      </c>
+      <c r="G175" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H175" s="40" t="str">
+        <f t="shared" si="13"/>
+        <v>188</v>
+      </c>
+      <c r="I175" s="37" t="s">
+        <v>556</v>
+      </c>
+      <c r="J175" s="12">
+        <f t="shared" si="14"/>
+        <v>392</v>
+      </c>
+      <c r="K175" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L175" s="12"/>
+      <c r="M175" s="12">
+        <v>0</v>
+      </c>
+      <c r="N175" s="12">
+        <v>1</v>
+      </c>
+      <c r="O175" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="P175" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="Q175" s="51"/>
+      <c r="R175" s="71"/>
+    </row>
+    <row r="176" customFormat="1" ht="20.25" spans="1:18">
+      <c r="A176" s="17"/>
+      <c r="B176" s="62"/>
+      <c r="C176" s="45"/>
+      <c r="D176" s="57" t="s">
+        <v>179</v>
+      </c>
+      <c r="E176" s="64" t="s">
+        <v>179</v>
+      </c>
+      <c r="F176" s="26">
+        <v>130</v>
+      </c>
+      <c r="G176" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H176" s="27" t="str">
+        <f t="shared" si="13"/>
+        <v>18A</v>
+      </c>
+      <c r="I176" s="30"/>
+      <c r="J176" s="31">
+        <f t="shared" si="14"/>
+        <v>394</v>
+      </c>
+      <c r="K176" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L176" s="12"/>
+      <c r="M176" s="12">
+        <v>0</v>
+      </c>
+      <c r="N176" s="12">
+        <v>1</v>
+      </c>
+      <c r="O176" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="P176" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="Q176" s="34"/>
+      <c r="R176" s="71"/>
+    </row>
+    <row r="177" customFormat="1" ht="20.25" spans="1:19">
+      <c r="A177" s="17"/>
+      <c r="B177" s="62"/>
+      <c r="C177" s="54"/>
+      <c r="D177" s="65" t="s">
+        <v>571</v>
+      </c>
+      <c r="E177" s="65"/>
+      <c r="F177" s="66"/>
+      <c r="G177" s="66"/>
+      <c r="H177" s="66"/>
+      <c r="I177" s="65"/>
+      <c r="J177" s="68"/>
+      <c r="K177" s="12"/>
+      <c r="L177" s="12"/>
+      <c r="M177" s="12"/>
+      <c r="N177" s="12"/>
+      <c r="O177" s="12"/>
+      <c r="P177" s="12"/>
+      <c r="Q177" s="12">
+        <f>SUM(F176,J176)</f>
+        <v>524</v>
+      </c>
+      <c r="R177" s="33"/>
+      <c r="S177" s="71"/>
+    </row>
+    <row r="178" ht="16.5" spans="19:19">
+      <c r="S178" s="72"/>
+    </row>
+    <row r="179" ht="16.5" spans="6:6">
+      <c r="F179" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="23">
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="D174:J174"/>
+    <mergeCell ref="D177:J177"/>
     <mergeCell ref="A3:A132"/>
-    <mergeCell ref="A133:A174"/>
+    <mergeCell ref="A133:A177"/>
     <mergeCell ref="B3:B50"/>
     <mergeCell ref="B51:B81"/>
     <mergeCell ref="B82:B113"/>
     <mergeCell ref="B114:B126"/>
     <mergeCell ref="B127:B132"/>
-    <mergeCell ref="B133:B143"/>
-    <mergeCell ref="B144:B174"/>
+    <mergeCell ref="B133:B146"/>
+    <mergeCell ref="B147:B177"/>
     <mergeCell ref="C3:C50"/>
     <mergeCell ref="C51:C81"/>
     <mergeCell ref="C82:C113"/>
     <mergeCell ref="C114:C126"/>
     <mergeCell ref="C127:C132"/>
-    <mergeCell ref="C133:C143"/>
-    <mergeCell ref="C144:C174"/>
+    <mergeCell ref="C133:C146"/>
+    <mergeCell ref="C147:C177"/>
     <mergeCell ref="Q99:Q102"/>
-    <mergeCell ref="Q168:Q172"/>
+    <mergeCell ref="Q171:Q175"/>
     <mergeCell ref="R99:R102"/>
-    <mergeCell ref="R144:R145"/>
-    <mergeCell ref="R146:R147"/>
+    <mergeCell ref="R147:R148"/>
+    <mergeCell ref="R149:R150"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Backend/srvdata/T-MAXeeprom.xlsx
+++ b/Backend/srvdata/T-MAXeeprom.xlsx
@@ -2143,10 +2143,10 @@
     <t>/*WIRELESS_PERIPHERAL_TYPE*/</t>
   </si>
   <si>
-    <t>0.关，1.WiFi，2.Bluetooth</t>
-  </si>
-  <si>
-    <t>0.关，1.WiFi，2.blue</t>
+    <t>0.OFF，1.WiFi，2.Bluetooth</t>
+  </si>
+  <si>
+    <t>0.OFF，1.WiFi，2.blue</t>
   </si>
   <si>
     <t>无线外设类型</t>
@@ -4951,7 +4951,8 @@
     <col min="5" max="5" width="62.2" style="5" customWidth="1"/>
     <col min="6" max="6" width="6.125" customWidth="1"/>
     <col min="7" max="7" width="3.5" customWidth="1"/>
-    <col min="8" max="9" width="13.5" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="9" max="9" width="21.6083333333333" customWidth="1"/>
     <col min="10" max="12" width="8.625" customWidth="1"/>
     <col min="13" max="14" width="12.75" customWidth="1"/>
     <col min="15" max="15" width="26.375" customWidth="1"/>
@@ -11002,7 +11003,7 @@
       </c>
       <c r="L120" s="13"/>
       <c r="M120" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N120" s="13" t="s">
         <v>136</v>
